--- a/base_dados/base-dados-pesquisa/2024/ibovespa_magic_formula_2024.xlsx
+++ b/base_dados/base-dados-pesquisa/2024/ibovespa_magic_formula_2024.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="161">
   <si>
     <t>ativo</t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t>ROA</t>
+  </si>
+  <si>
+    <t>giro_ativo</t>
+  </si>
+  <si>
+    <t>alavancagem</t>
   </si>
   <si>
     <t>AXIA ENERGIA S.A.</t>
@@ -848,10 +854,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P207"/>
+  <dimension ref="A1:R207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -900,25 +906,31 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D2">
-        <v>29.87531280517578</v>
+        <v>29.87531471252441</v>
       </c>
       <c r="E2">
         <v>2250447</v>
       </c>
       <c r="F2">
-        <v>67232808.07646942</v>
+        <v>67232812.36885643</v>
       </c>
       <c r="G2">
         <v>1142962</v>
@@ -930,13 +942,13 @@
         <v>112582272</v>
       </c>
       <c r="J2">
-        <v>97279867.07646942</v>
+        <v>97279871.36885643</v>
       </c>
       <c r="K2">
         <v>0.008013513012972066</v>
       </c>
       <c r="L2">
-        <v>0.01174921424493255</v>
+        <v>0.01174921372650902</v>
       </c>
       <c r="M2">
         <v>0.002913877950517822</v>
@@ -950,16 +962,22 @@
       <c r="P2">
         <v>0.001919545445534356</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2">
+        <v>8.579268260857221E-05</v>
+      </c>
+      <c r="R2">
+        <v>0.2085786585488447</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D3">
         <v>27.16487693786621</v>
@@ -1000,25 +1018,31 @@
       <c r="P3">
         <v>0.009876404653284909</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3">
+        <v>8.45079605011915E-05</v>
+      </c>
+      <c r="R3">
+        <v>0.2347496983285437</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D4">
-        <v>29.61039352416992</v>
+        <v>29.70523643493652</v>
       </c>
       <c r="E4">
         <v>2248880</v>
       </c>
       <c r="F4">
-        <v>66590221.78863525</v>
+        <v>66803512.11380005</v>
       </c>
       <c r="G4">
         <v>8699292</v>
@@ -1030,13 +1054,13 @@
         <v>121252094</v>
       </c>
       <c r="J4">
-        <v>102417962.7886353</v>
+        <v>102631253.1138</v>
       </c>
       <c r="K4">
         <v>0.05538134159613804</v>
       </c>
       <c r="L4">
-        <v>0.08493912359839784</v>
+        <v>0.08476260141103424</v>
       </c>
       <c r="M4">
         <v>0.05939624432382998</v>
@@ -1050,25 +1074,31 @@
       <c r="P4">
         <v>0.03459897955306541</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4">
+        <v>0.01257544849455682</v>
+      </c>
+      <c r="R4">
+        <v>0.2312001301228354</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D5">
-        <v>39.31481552124023</v>
+        <v>39.31481170654297</v>
       </c>
       <c r="E5">
         <v>2285652288</v>
       </c>
       <c r="F5">
-        <v>89859998048.42065</v>
+        <v>89859989329.34912</v>
       </c>
       <c r="G5">
         <v>966561</v>
@@ -1080,13 +1110,13 @@
         <v>15247518</v>
       </c>
       <c r="J5">
-        <v>89870214150.42065</v>
+        <v>89870205431.34912</v>
       </c>
       <c r="K5">
         <v>0.037958507077941</v>
       </c>
       <c r="L5">
-        <v>1.075507618555592E-05</v>
+        <v>1.075507722899716E-05</v>
       </c>
       <c r="M5">
         <v>0.05915461126197719</v>
@@ -1100,16 +1130,22 @@
       <c r="P5">
         <v>0.03378366306478043</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5">
+        <v>0.003128906990190815</v>
+      </c>
+      <c r="R5">
+        <v>0.3872958046030246</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D6">
         <v>37.46692657470703</v>
@@ -1150,25 +1186,31 @@
       <c r="P6">
         <v>0.01791315055414247</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6">
+        <v>0.003197298571818775</v>
+      </c>
+      <c r="R6">
+        <v>0.3960232994852214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D7">
-        <v>37.59054565429688</v>
+        <v>38.01016998291016</v>
       </c>
       <c r="E7">
         <v>2285652288</v>
       </c>
       <c r="F7">
-        <v>85918916681.91211</v>
+        <v>86878031988.70752</v>
       </c>
       <c r="G7">
         <v>550422</v>
@@ -1180,13 +1222,13 @@
         <v>16229287</v>
       </c>
       <c r="J7">
-        <v>85929040003.91211</v>
+        <v>86888155310.70752</v>
       </c>
       <c r="K7">
         <v>0.02088681238354806</v>
       </c>
       <c r="L7">
-        <v>6.405541129924655E-06</v>
+        <v>6.334833534349067E-06</v>
       </c>
       <c r="M7">
         <v>0.03406674612384389</v>
@@ -1200,25 +1242,31 @@
       <c r="P7">
         <v>0.02014373826384111</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7">
+        <v>0.003536382324821427</v>
+      </c>
+      <c r="R7">
+        <v>0.3738362942304197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D8">
-        <v>27.71806335449219</v>
+        <v>27.71806526184082</v>
       </c>
       <c r="E8">
         <v>641762</v>
       </c>
       <c r="F8">
-        <v>17788399.77450562</v>
+        <v>17788400.99856949</v>
       </c>
       <c r="G8">
         <v>629825</v>
@@ -1230,19 +1278,19 @@
         <v>12505049</v>
       </c>
       <c r="J8">
-        <v>17412372.77450562</v>
+        <v>17412373.99856949</v>
       </c>
       <c r="K8">
         <v>0.05192710508728569</v>
       </c>
       <c r="L8">
-        <v>0.03617111855784298</v>
+        <v>0.0361711160150674</v>
       </c>
       <c r="M8">
         <v>0.05206041175848251</v>
       </c>
       <c r="N8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1250,25 +1298,31 @@
       <c r="P8">
         <v>0.04644385788401213</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D9">
-        <v>27.77455902099609</v>
+        <v>27.77455711364746</v>
       </c>
       <c r="E9">
         <v>641705932</v>
       </c>
       <c r="F9">
-        <v>17823099282.45731</v>
+        <v>17823098058.50037</v>
       </c>
       <c r="G9">
         <v>552196</v>
@@ -1280,19 +1334,19 @@
         <v>12897574</v>
       </c>
       <c r="J9">
-        <v>17823016984.45731</v>
+        <v>17823015760.50037</v>
       </c>
       <c r="K9">
         <v>0.04308888860450606</v>
       </c>
       <c r="L9">
-        <v>3.098218446863102E-05</v>
+        <v>3.09821865962653E-05</v>
       </c>
       <c r="M9">
         <v>0.04527820503297752</v>
       </c>
       <c r="N9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1300,25 +1354,31 @@
       <c r="P9">
         <v>0.0418404019287686</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D10">
-        <v>33.0912971496582</v>
+        <v>32.71026611328125</v>
       </c>
       <c r="E10">
         <v>641740</v>
       </c>
       <c r="F10">
-        <v>21236009.03282166</v>
+        <v>20991486.17553711</v>
       </c>
       <c r="G10">
         <v>680933</v>
@@ -1330,19 +1390,19 @@
         <v>13418939</v>
       </c>
       <c r="J10">
-        <v>21190172.03282166</v>
+        <v>20945649.17553711</v>
       </c>
       <c r="K10">
         <v>0.05091810411675616</v>
       </c>
       <c r="L10">
-        <v>0.03213437809496292</v>
+        <v>0.03250951996251693</v>
       </c>
       <c r="M10">
         <v>0.05507760337832969</v>
       </c>
       <c r="N10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1350,16 +1410,22 @@
       <c r="P10">
         <v>0.05038777870209386</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D11">
         <v>21.08846092224121</v>
@@ -1400,25 +1466,31 @@
       <c r="P11">
         <v>0.01379026635037025</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11">
+        <v>0.01112768205631743</v>
+      </c>
+      <c r="R11">
+        <v>0.2617060123628288</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D12">
-        <v>19.71989440917969</v>
+        <v>19.71989631652832</v>
       </c>
       <c r="E12">
         <v>1849912751</v>
       </c>
       <c r="F12">
-        <v>36480084115.91512</v>
+        <v>36480087644.34367</v>
       </c>
       <c r="G12">
         <v>-1607520</v>
@@ -1430,13 +1502,13 @@
         <v>14309342</v>
       </c>
       <c r="J12">
-        <v>36483338136.91512</v>
+        <v>36483341665.34367</v>
       </c>
       <c r="K12">
         <v>-0.09152689037970689</v>
       </c>
       <c r="L12">
-        <v>-4.40617575608701E-05</v>
+        <v>-4.406175329950706E-05</v>
       </c>
       <c r="M12">
         <v>-0.1219009930715193</v>
@@ -1450,25 +1522,31 @@
       <c r="P12">
         <v>-0.06991310976770621</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12">
+        <v>0.009328505519267234</v>
+      </c>
+      <c r="R12">
+        <v>0.270597522151418</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D13">
-        <v>19.03464889526367</v>
+        <v>19.10126876831055</v>
       </c>
       <c r="E13">
         <v>1850667346</v>
       </c>
       <c r="F13">
-        <v>35226803153.03945</v>
+        <v>35350094376.68197</v>
       </c>
       <c r="G13">
         <v>807518</v>
@@ -1480,13 +1558,13 @@
         <v>14987441</v>
       </c>
       <c r="J13">
-        <v>35230655712.03945</v>
+        <v>35353946935.68197</v>
       </c>
       <c r="K13">
         <v>0.04286188959660298</v>
       </c>
       <c r="L13">
-        <v>2.292089044837292E-05</v>
+        <v>2.284095751654223E-05</v>
       </c>
       <c r="M13">
         <v>0.04542549992356934</v>
@@ -1500,25 +1578,31 @@
       <c r="P13">
         <v>0.02623933482146178</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13">
+        <v>0.009582121677220477</v>
+      </c>
+      <c r="R13">
+        <v>0.2679415130602561</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D14">
-        <v>14.65405464172363</v>
+        <v>14.65405368804932</v>
       </c>
       <c r="E14">
         <v>2420249036</v>
       </c>
       <c r="F14">
-        <v>35466461620.12295</v>
+        <v>35466459311.99361</v>
       </c>
       <c r="G14">
         <v>1112928</v>
@@ -1530,13 +1614,13 @@
         <v>25025216</v>
       </c>
       <c r="J14">
-        <v>35467724820.12295</v>
+        <v>35467722511.99361</v>
       </c>
       <c r="K14">
         <v>0.04233530084125266</v>
       </c>
       <c r="L14">
-        <v>3.137861268644359E-05</v>
+        <v>3.137861472846635E-05</v>
       </c>
       <c r="M14">
         <v>0.02075598468360872</v>
@@ -1550,16 +1634,22 @@
       <c r="P14">
         <v>0.009559771582740963</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14">
+        <v>0.1121857617317166</v>
+      </c>
+      <c r="R14">
+        <v>0.05977596303532166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D15">
         <v>13.56826019287109</v>
@@ -1600,25 +1690,31 @@
       <c r="P15">
         <v>0.01445775703117671</v>
       </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15">
+        <v>0.1166388366903977</v>
+      </c>
+      <c r="R15">
+        <v>0.05729923983422418</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D16">
-        <v>16.1099796295166</v>
+        <v>16.09277534484863</v>
       </c>
       <c r="E16">
         <v>2420410636</v>
       </c>
       <c r="F16">
-        <v>38992766041.02532</v>
+        <v>38951124607.4302</v>
       </c>
       <c r="G16">
         <v>1431185</v>
@@ -1630,13 +1726,13 @@
         <v>25977252</v>
       </c>
       <c r="J16">
-        <v>38993612070.02532</v>
+        <v>38951970636.4302</v>
       </c>
       <c r="K16">
         <v>0.0533560752690918</v>
       </c>
       <c r="L16">
-        <v>3.670306298964702E-05</v>
+        <v>3.674230023837281E-05</v>
       </c>
       <c r="M16">
         <v>0.03098965202323941</v>
@@ -1650,16 +1746,22 @@
       <c r="P16">
         <v>0.01476139462178898</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16">
+        <v>0.1177012303674291</v>
+      </c>
+      <c r="R16">
+        <v>0.05745497498308638</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D17">
         <v>32.2434196472168</v>
@@ -1700,16 +1802,22 @@
       <c r="P17">
         <v>0.07934131651453917</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17">
+        <v>5.967022256993018E-06</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D18">
         <v>30.3167781829834</v>
@@ -1750,25 +1858,31 @@
       <c r="P18">
         <v>0.05093696576598374</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18">
+        <v>6.106916402712169E-06</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D19">
-        <v>31.42830085754395</v>
+        <v>31.27083396911621</v>
       </c>
       <c r="E19">
         <v>1152254440</v>
       </c>
       <c r="F19">
-        <v>36213399204.76082</v>
+        <v>36031957283.41698</v>
       </c>
       <c r="G19">
         <v>1310612</v>
@@ -1780,13 +1894,13 @@
         <v>20423132</v>
       </c>
       <c r="J19">
-        <v>36213363189.76082</v>
+        <v>36031921268.41698</v>
       </c>
       <c r="K19">
         <v>0.06428628432357553</v>
       </c>
       <c r="L19">
-        <v>3.61913913693211E-05</v>
+        <v>3.637363631644004E-05</v>
       </c>
       <c r="M19">
         <v>0.06193761074452243</v>
@@ -1800,25 +1914,31 @@
       <c r="P19">
         <v>0.05945692815679152</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19">
+        <v>5.828373301481587E-06</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D20">
-        <v>25.44513130187988</v>
+        <v>25.44512939453125</v>
       </c>
       <c r="E20">
         <v>815927740</v>
       </c>
       <c r="F20">
-        <v>20761388477.14611</v>
+        <v>20761386920.88745</v>
       </c>
       <c r="G20">
         <v>2560470</v>
@@ -1830,13 +1950,13 @@
         <v>10778843</v>
       </c>
       <c r="J20">
-        <v>20767304172.14611</v>
+        <v>20767302615.88745</v>
       </c>
       <c r="K20">
         <v>0.1533717195408462</v>
       </c>
       <c r="L20">
-        <v>0.000123293325834472</v>
+        <v>0.0001232933350738186</v>
       </c>
       <c r="M20">
         <v>0.1562407022720342</v>
@@ -1850,16 +1970,22 @@
       <c r="P20">
         <v>0.06118037900727733</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20">
+        <v>0.04206047066809786</v>
+      </c>
+      <c r="R20">
+        <v>0.3151340583820778</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D21">
         <v>28.80310440063477</v>
@@ -1900,25 +2026,31 @@
       <c r="P21">
         <v>0.03041054223288724</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21">
+        <v>0.03488370631980277</v>
+      </c>
+      <c r="R21">
+        <v>0.311146586984283</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D22">
-        <v>28.29370307922363</v>
+        <v>28.60696983337402</v>
       </c>
       <c r="E22">
         <v>815927740</v>
       </c>
       <c r="F22">
-        <v>23085617209.66198</v>
+        <v>23341220244.39304</v>
       </c>
       <c r="G22">
         <v>995244</v>
@@ -1930,13 +2062,13 @@
         <v>10797402</v>
       </c>
       <c r="J22">
-        <v>23094748346.66198</v>
+        <v>23350351381.39304</v>
       </c>
       <c r="K22">
         <v>0.0499406404051998</v>
       </c>
       <c r="L22">
-        <v>4.309395300875181E-05</v>
+        <v>4.262222798039219E-05</v>
       </c>
       <c r="M22">
         <v>0.06066709380645455</v>
@@ -1950,25 +2082,31 @@
       <c r="P22">
         <v>0.02157728590658977</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22">
+        <v>0.03793923837448195</v>
+      </c>
+      <c r="R22">
+        <v>0.3612290712873574</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D23">
-        <v>21.48669052124023</v>
+        <v>21.48668670654297</v>
       </c>
       <c r="E23">
         <v>1652584004</v>
       </c>
       <c r="F23">
-        <v>35508561054.30003</v>
+        <v>35508554750.19235</v>
       </c>
       <c r="G23">
         <v>1898274</v>
@@ -1980,13 +2118,13 @@
         <v>68664676</v>
       </c>
       <c r="J23">
-        <v>35520549879.30003</v>
+        <v>35520543575.19235</v>
       </c>
       <c r="K23">
         <v>0.02353616366882821</v>
       </c>
       <c r="L23">
-        <v>5.344157132843934E-05</v>
+        <v>5.344158081313148E-05</v>
       </c>
       <c r="M23">
         <v>0.01304354803916937</v>
@@ -2000,25 +2138,31 @@
       <c r="P23">
         <v>0.007302358094903545</v>
       </c>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="Q23">
+        <v>0.106456110453687</v>
+      </c>
+      <c r="R23">
+        <v>0.1497864252410398</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D24">
-        <v>19.81035041809082</v>
+        <v>19.81035232543945</v>
       </c>
       <c r="E24">
         <v>1646940404</v>
       </c>
       <c r="F24">
-        <v>32626466520.95206</v>
+        <v>32626469662.24159</v>
       </c>
       <c r="G24">
         <v>2030760</v>
@@ -2030,13 +2174,13 @@
         <v>69086211</v>
       </c>
       <c r="J24">
-        <v>32638327866.95206</v>
+        <v>32638331008.24159</v>
       </c>
       <c r="K24">
         <v>0.0250873537789411</v>
       </c>
       <c r="L24">
-        <v>6.222009927341425E-05</v>
+        <v>6.222009328501532E-05</v>
       </c>
       <c r="M24">
         <v>0.01768558417540079</v>
@@ -2050,25 +2194,31 @@
       <c r="P24">
         <v>0.009946411179068354</v>
       </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="Q24">
+        <v>0.1074762710896919</v>
+      </c>
+      <c r="R24">
+        <v>0.1526499818969667</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D25">
-        <v>24.70425415039062</v>
+        <v>24.60688781738281</v>
       </c>
       <c r="E25">
         <v>1632616504</v>
       </c>
       <c r="F25">
-        <v>40332573044.93823</v>
+        <v>40173611162.73572</v>
       </c>
       <c r="G25">
         <v>2277281</v>
@@ -2080,13 +2230,13 @@
         <v>69028553</v>
       </c>
       <c r="J25">
-        <v>40345331495.93823</v>
+        <v>40186369613.73572</v>
       </c>
       <c r="K25">
         <v>0.02784404475801559</v>
       </c>
       <c r="L25">
-        <v>5.644472149718897E-05</v>
+        <v>5.666799519062863E-05</v>
       </c>
       <c r="M25">
         <v>0.02415585909790113</v>
@@ -2100,25 +2250,31 @@
       <c r="P25">
         <v>0.01362491895148025</v>
       </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="Q25">
+        <v>0.1108718909903854</v>
+      </c>
+      <c r="R25">
+        <v>0.1558716927993762</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D26">
-        <v>2.006177186965942</v>
+        <v>2.006176948547363</v>
       </c>
       <c r="E26">
         <v>1871956123</v>
       </c>
       <c r="F26">
-        <v>3755475668.963812</v>
+        <v>3755475222.654693</v>
       </c>
       <c r="G26">
         <v>79207</v>
@@ -2130,19 +2286,19 @@
         <v>11648430</v>
       </c>
       <c r="J26">
-        <v>3758895936.963812</v>
+        <v>3758895490.654693</v>
       </c>
       <c r="K26">
         <v>0.005256393087179794</v>
       </c>
       <c r="L26">
-        <v>2.107187890494733E-05</v>
+        <v>2.107188140689817E-05</v>
       </c>
       <c r="M26">
         <v>-0.0007307422545355898</v>
       </c>
       <c r="N26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O26">
         <v>47.07493024606411</v>
@@ -2150,16 +2306,22 @@
       <c r="P26">
         <v>-0.0005295571199085419</v>
       </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0.2319714014270046</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D27">
         <v>1.504632472991943</v>
@@ -2192,7 +2354,7 @@
         <v>-0.0007150749376886586</v>
       </c>
       <c r="N27" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O27">
         <v>30.573286728825</v>
@@ -2200,25 +2362,31 @@
       <c r="P27">
         <v>-0.0005222080189671172</v>
       </c>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0.2244335134587135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D28">
-        <v>1.088096022605896</v>
+        <v>1.13059937953949</v>
       </c>
       <c r="E28">
         <v>1873234623</v>
       </c>
       <c r="F28">
-        <v>2038259142.693955</v>
+        <v>2117877902.49569</v>
       </c>
       <c r="G28">
         <v>31661</v>
@@ -2230,19 +2398,19 @@
         <v>11616160</v>
       </c>
       <c r="J28">
-        <v>2041744672.693955</v>
+        <v>2121363432.49569</v>
       </c>
       <c r="K28">
         <v>0.002096520323222103</v>
       </c>
       <c r="L28">
-        <v>1.550683610121793E-05</v>
+        <v>1.492483537474399E-05</v>
       </c>
       <c r="M28">
         <v>-0.002506938609661024</v>
       </c>
       <c r="N28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O28">
         <v>110.1173367865829</v>
@@ -2250,16 +2418,22 @@
       <c r="P28">
         <v>-0.001839146867254786</v>
       </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0.2201863815345891</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E29">
         <v>2016918425</v>
@@ -2288,16 +2462,22 @@
       <c r="P29">
         <v>0.01695818395335724</v>
       </c>
-    </row>
-    <row r="30" spans="1:16">
+      <c r="Q29">
+        <v>0.0009069747266789156</v>
+      </c>
+      <c r="R29">
+        <v>0.2797280578076133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E30">
         <v>2017983050</v>
@@ -2326,16 +2506,22 @@
       <c r="P30">
         <v>0.01338434825491981</v>
       </c>
-    </row>
-    <row r="31" spans="1:16">
+      <c r="Q30">
+        <v>0.001067492779224869</v>
+      </c>
+      <c r="R30">
+        <v>0.2763046376314359</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E31">
         <v>2017986384</v>
@@ -2364,25 +2550,31 @@
       <c r="P31">
         <v>0.0206648434114297</v>
       </c>
-    </row>
-    <row r="32" spans="1:16">
+      <c r="Q31">
+        <v>0.0006860956792768353</v>
+      </c>
+      <c r="R31">
+        <v>0.2627823331954058</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D32">
-        <v>29.84381103515625</v>
+        <v>29.84380722045898</v>
       </c>
       <c r="E32">
         <v>633057136</v>
       </c>
       <c r="F32">
-        <v>18892837541.24121</v>
+        <v>18892835126.31989</v>
       </c>
       <c r="G32">
         <v>599448</v>
@@ -2394,13 +2586,13 @@
         <v>11711379</v>
       </c>
       <c r="J32">
-        <v>18900453940.24121</v>
+        <v>18900451525.31989</v>
       </c>
       <c r="K32">
         <v>0.0310148429891941</v>
       </c>
       <c r="L32">
-        <v>3.171606364033973E-05</v>
+        <v>3.171606769271902E-05</v>
       </c>
       <c r="M32">
         <v>0.03349221300070641</v>
@@ -2414,25 +2606,31 @@
       <c r="P32">
         <v>0.015890518443964</v>
       </c>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="Q32">
+        <v>0.07444390275086978</v>
+      </c>
+      <c r="R32">
+        <v>0.4285982013702696</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D33">
-        <v>26.26784706115723</v>
+        <v>26.26784896850586</v>
       </c>
       <c r="E33">
         <v>632257519</v>
       </c>
       <c r="F33">
-        <v>16608043812.35871</v>
+        <v>16608045018.29422</v>
       </c>
       <c r="G33">
         <v>701920</v>
@@ -2444,13 +2642,13 @@
         <v>12014866</v>
       </c>
       <c r="J33">
-        <v>16615680993.35871</v>
+        <v>16615682199.29422</v>
       </c>
       <c r="K33">
         <v>0.03571739880329006</v>
       </c>
       <c r="L33">
-        <v>4.224443164746348E-05</v>
+        <v>4.224442858144068E-05</v>
       </c>
       <c r="M33">
         <v>0.04101702008162222</v>
@@ -2464,25 +2662,31 @@
       <c r="P33">
         <v>0.01985221317287443</v>
       </c>
-    </row>
-    <row r="34" spans="1:16">
+      <c r="Q33">
+        <v>0.08916246584875831</v>
+      </c>
+      <c r="R33">
+        <v>0.4095284451816124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D34">
-        <v>24.26345252990723</v>
+        <v>24.69821929931641</v>
       </c>
       <c r="E34">
         <v>632682269</v>
       </c>
       <c r="F34">
-        <v>15351056200.39549</v>
+        <v>15626125426.55109</v>
       </c>
       <c r="G34">
         <v>514423</v>
@@ -2494,13 +2698,13 @@
         <v>12214790</v>
       </c>
       <c r="J34">
-        <v>15358460454.39549</v>
+        <v>15633529680.55109</v>
       </c>
       <c r="K34">
         <v>0.02622059464263396</v>
       </c>
       <c r="L34">
-        <v>3.34944379045997E-05</v>
+        <v>3.29051091155677E-05</v>
       </c>
       <c r="M34">
         <v>0.03081330092453493</v>
@@ -2514,25 +2718,31 @@
       <c r="P34">
         <v>0.01489931901302631</v>
       </c>
-    </row>
-    <row r="35" spans="1:16">
+      <c r="Q34">
+        <v>0.07692618899576639</v>
+      </c>
+      <c r="R34">
+        <v>0.4060734424976772</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D35">
-        <v>20.98309516906738</v>
+        <v>20.98309135437012</v>
       </c>
       <c r="E35">
         <v>658883304</v>
       </c>
       <c r="F35">
-        <v>13825411073.14156</v>
+        <v>13825408559.70122</v>
       </c>
       <c r="G35">
         <v>1076792</v>
@@ -2544,13 +2754,13 @@
         <v>18016198</v>
       </c>
       <c r="J35">
-        <v>13834472507.14156</v>
+        <v>13834469993.70122</v>
       </c>
       <c r="K35">
         <v>0.03976684519532579</v>
       </c>
       <c r="L35">
-        <v>7.783397592095718E-05</v>
+        <v>7.783399006179921E-05</v>
       </c>
       <c r="M35">
         <v>0.03569443453052636</v>
@@ -2564,25 +2774,31 @@
       <c r="P35">
         <v>0.01752398137113345</v>
       </c>
-    </row>
-    <row r="36" spans="1:16">
+      <c r="Q35">
+        <v>0.04513262191873532</v>
+      </c>
+      <c r="R35">
+        <v>0.2797473560936519</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D36">
-        <v>22.20048332214355</v>
+        <v>22.20048141479492</v>
       </c>
       <c r="E36">
         <v>658883304</v>
       </c>
       <c r="F36">
-        <v>14627527801.69084</v>
+        <v>14627526544.97067</v>
       </c>
       <c r="G36">
         <v>926884</v>
@@ -2594,13 +2810,13 @@
         <v>18604578</v>
       </c>
       <c r="J36">
-        <v>14638842510.69084</v>
+        <v>14638841253.97067</v>
       </c>
       <c r="K36">
         <v>0.0309794815631803</v>
       </c>
       <c r="L36">
-        <v>6.33167546766823E-05</v>
+        <v>6.331676011232035E-05</v>
       </c>
       <c r="M36">
         <v>0.02883376338877452</v>
@@ -2614,25 +2830,31 @@
       <c r="P36">
         <v>0.01437396241006795</v>
       </c>
-    </row>
-    <row r="37" spans="1:16">
+      <c r="Q36">
+        <v>0.03568260338171823</v>
+      </c>
+      <c r="R36">
+        <v>0.3041380554191759</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D37">
-        <v>20.54347610473633</v>
+        <v>20.47584342956543</v>
       </c>
       <c r="E37">
         <v>658883304</v>
       </c>
       <c r="F37">
-        <v>13535753411.53372</v>
+        <v>13491191371.05876</v>
       </c>
       <c r="G37">
         <v>1843456</v>
@@ -2644,13 +2866,13 @@
         <v>19724728</v>
       </c>
       <c r="J37">
-        <v>13547161562.53372</v>
+        <v>13502599522.05876</v>
       </c>
       <c r="K37">
         <v>0.05921251291921958</v>
       </c>
       <c r="L37">
-        <v>0.0001360769185109813</v>
+        <v>0.0001365260072320449</v>
       </c>
       <c r="M37">
         <v>0.05613253576931454</v>
@@ -2664,16 +2886,22 @@
       <c r="P37">
         <v>0.02821249213689462</v>
       </c>
-    </row>
-    <row r="38" spans="1:16">
+      <c r="Q37">
+        <v>0.03649795715330907</v>
+      </c>
+      <c r="R37">
+        <v>0.2915967033856626</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D38">
         <v>30.0604248046875</v>
@@ -2706,7 +2934,7 @@
         <v>0.01306062308021881</v>
       </c>
       <c r="N38" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O38">
         <v>6.157864869977211</v>
@@ -2714,16 +2942,22 @@
       <c r="P38">
         <v>0.01148798666851717</v>
       </c>
-    </row>
-    <row r="39" spans="1:16">
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0.08431334115190905</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C39" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D39">
         <v>28.77869606018066</v>
@@ -2756,7 +2990,7 @@
         <v>0.02263241787606442</v>
       </c>
       <c r="N39" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O39">
         <v>4.818684457699495</v>
@@ -2764,25 +2998,31 @@
       <c r="P39">
         <v>0.02044517760449799</v>
       </c>
-    </row>
-    <row r="40" spans="1:16">
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0.08003821775038551</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C40" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D40">
-        <v>30.47597312927246</v>
+        <v>30.41970825195312</v>
       </c>
       <c r="E40">
         <v>1171152221</v>
       </c>
       <c r="F40">
-        <v>35692003617.48376</v>
+        <v>35626108881.44693</v>
       </c>
       <c r="G40">
         <v>757398</v>
@@ -2794,19 +3034,19 @@
         <v>25676500</v>
       </c>
       <c r="J40">
-        <v>35694034762.48376</v>
+        <v>35628140026.44693</v>
       </c>
       <c r="K40">
         <v>0.02733534372914046</v>
       </c>
       <c r="L40">
-        <v>2.121917583820094E-05</v>
+        <v>2.125842099637478E-05</v>
       </c>
       <c r="M40">
         <v>0.02960181488910093</v>
       </c>
       <c r="N40" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O40">
         <v>2.710367600653818</v>
@@ -2814,25 +3054,31 @@
       <c r="P40">
         <v>0.02700203807265662</v>
       </c>
-    </row>
-    <row r="41" spans="1:16">
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0.07292807225979872</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D41">
-        <v>15.41346168518066</v>
+        <v>15.41346073150635</v>
       </c>
       <c r="E41">
         <v>393097</v>
       </c>
       <c r="F41">
-        <v>6058985.548059464</v>
+        <v>6058985.173172951</v>
       </c>
       <c r="G41">
         <v>333551</v>
@@ -2844,19 +3090,19 @@
         <v>8214079</v>
       </c>
       <c r="J41">
-        <v>5348106.548059464</v>
+        <v>5348106.173172951</v>
       </c>
       <c r="K41">
         <v>0.04445449941358354</v>
       </c>
       <c r="L41">
-        <v>0.06236805437637129</v>
+        <v>0.06236805874818847</v>
       </c>
       <c r="M41">
         <v>0.04176950331254423</v>
       </c>
       <c r="N41" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -2864,25 +3110,31 @@
       <c r="P41">
         <v>0.04146485014677748</v>
       </c>
-    </row>
-    <row r="42" spans="1:16">
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D42">
-        <v>14.66443824768066</v>
+        <v>14.66443729400635</v>
       </c>
       <c r="E42">
         <v>393097</v>
       </c>
       <c r="F42">
-        <v>5764546.681848526</v>
+        <v>5764546.306962013</v>
       </c>
       <c r="G42">
         <v>518417</v>
@@ -2894,19 +3146,19 @@
         <v>8451831</v>
       </c>
       <c r="J42">
-        <v>5469815.681848526</v>
+        <v>5469815.306962013</v>
       </c>
       <c r="K42">
         <v>0.0635540817202192</v>
       </c>
       <c r="L42">
-        <v>0.09477778231547297</v>
+        <v>0.0947777888112887</v>
       </c>
       <c r="M42">
         <v>0.06335467427117272</v>
       </c>
       <c r="N42" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -2914,25 +3166,31 @@
       <c r="P42">
         <v>0.06293239629863773</v>
       </c>
-    </row>
-    <row r="43" spans="1:16">
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D43">
-        <v>16.01917457580566</v>
+        <v>16.08255386352539</v>
       </c>
       <c r="E43">
         <v>393097</v>
       </c>
       <c r="F43">
-        <v>6297089.468225479</v>
+        <v>6322003.67609024</v>
       </c>
       <c r="G43">
         <v>463833</v>
@@ -2944,19 +3202,19 @@
         <v>8808159</v>
       </c>
       <c r="J43">
-        <v>5739158.468225479</v>
+        <v>5764072.67609024</v>
       </c>
       <c r="K43">
         <v>0.05622062808446021</v>
       </c>
       <c r="L43">
-        <v>0.08081899159397406</v>
+        <v>0.08046966547177838</v>
       </c>
       <c r="M43">
         <v>0.04547828893642815</v>
       </c>
       <c r="N43" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -2964,16 +3222,22 @@
       <c r="P43">
         <v>0.04491055894799555</v>
       </c>
-    </row>
-    <row r="44" spans="1:16">
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C44" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D44">
         <v>8.835201263427734</v>
@@ -3014,16 +3278,22 @@
       <c r="P44">
         <v>0.001120544621406396</v>
       </c>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="Q44">
+        <v>0.03832048581867194</v>
+      </c>
+      <c r="R44">
+        <v>0.2417573678564676</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C45" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D45">
         <v>10.59195709228516</v>
@@ -3064,25 +3334,31 @@
       <c r="P45">
         <v>0.001316599156107529</v>
       </c>
-    </row>
-    <row r="46" spans="1:16">
+      <c r="Q45">
+        <v>0.04165429799989574</v>
+      </c>
+      <c r="R45">
+        <v>0.2468634947814708</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C46" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D46">
-        <v>11.6888599395752</v>
+        <v>11.86025047302246</v>
       </c>
       <c r="E46">
         <v>888574972</v>
       </c>
       <c r="F46">
-        <v>10386428393.51995</v>
+        <v>10538721731.97892</v>
       </c>
       <c r="G46">
         <v>774491</v>
@@ -3094,13 +3370,13 @@
         <v>5383429</v>
       </c>
       <c r="J46">
-        <v>10401039826.51995</v>
+        <v>10553333164.97892</v>
       </c>
       <c r="K46">
         <v>0.03873450089327948</v>
       </c>
       <c r="L46">
-        <v>7.446284341929439E-05</v>
+        <v>7.338828291426798E-05</v>
       </c>
       <c r="M46">
         <v>0.01470085330372147</v>
@@ -3114,16 +3390,22 @@
       <c r="P46">
         <v>0.001351619185679371</v>
       </c>
-    </row>
-    <row r="47" spans="1:16">
+      <c r="Q46">
+        <v>0.05034685399409609</v>
+      </c>
+      <c r="R46">
+        <v>0.2500894450105533</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D47">
         <v>12.75</v>
@@ -3164,16 +3446,22 @@
       <c r="P47">
         <v>-0.002314828542116468</v>
       </c>
-    </row>
-    <row r="48" spans="1:16">
+      <c r="Q47">
+        <v>0.006177779926839649</v>
+      </c>
+      <c r="R47">
+        <v>0.4292768827492624</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C48" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D48">
         <v>12.69999980926514</v>
@@ -3214,25 +3502,31 @@
       <c r="P48">
         <v>0.02970486517191833</v>
       </c>
-    </row>
-    <row r="49" spans="1:16">
+      <c r="Q48">
+        <v>0.01683903052984484</v>
+      </c>
+      <c r="R48">
+        <v>0.4293726957819583</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
       <c r="A49" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D49">
-        <v>13.97000026702881</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="E49">
         <v>1583496</v>
       </c>
       <c r="F49">
-        <v>22121439.54283905</v>
+        <v>22184779.32243347</v>
       </c>
       <c r="G49">
         <v>394763</v>
@@ -3244,13 +3538,13 @@
         <v>15047206</v>
       </c>
       <c r="J49">
-        <v>34881414.54283905</v>
+        <v>34944754.32243347</v>
       </c>
       <c r="K49">
         <v>0.01419644084022757</v>
       </c>
       <c r="L49">
-        <v>0.01131728759208369</v>
+        <v>0.01129677422704255</v>
       </c>
       <c r="M49">
         <v>0.006823725281623711</v>
@@ -3264,16 +3558,22 @@
       <c r="P49">
         <v>0.002729262517001074</v>
       </c>
-    </row>
-    <row r="50" spans="1:16">
+      <c r="Q49">
+        <v>0.0326121326640928</v>
+      </c>
+      <c r="R49">
+        <v>0.3515039890325528</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
       <c r="A50" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D50">
         <v>55.5</v>
@@ -3306,7 +3606,7 @@
         <v>0.001327461729551041</v>
       </c>
       <c r="N50" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O50">
         <v>48.01145693366605</v>
@@ -3314,16 +3614,22 @@
       <c r="P50">
         <v>0.001118545021338581</v>
       </c>
-    </row>
-    <row r="51" spans="1:16">
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0.1500058542964067</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C51" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D51">
         <v>57.45000076293945</v>
@@ -3356,7 +3662,7 @@
         <v>-0.007821873482193256</v>
       </c>
       <c r="N51" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O51">
         <v>-39.42472597745664</v>
@@ -3364,16 +3670,22 @@
       <c r="P51">
         <v>-0.006455610037898726</v>
       </c>
-    </row>
-    <row r="52" spans="1:16">
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0.1675036401171764</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
       <c r="A52" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C52" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D52">
         <v>60</v>
@@ -3406,7 +3718,7 @@
         <v>-0.001669072485105013</v>
       </c>
       <c r="N52" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O52">
         <v>180.9071118851294</v>
@@ -3414,16 +3726,22 @@
       <c r="P52">
         <v>-0.001370143800607228</v>
       </c>
-    </row>
-    <row r="53" spans="1:16">
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0.1716411003888681</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C53" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D53">
         <v>19.49953842163086</v>
@@ -3464,16 +3782,22 @@
       <c r="P53">
         <v>0.004857790951757568</v>
       </c>
-    </row>
-    <row r="54" spans="1:16">
+      <c r="Q53">
+        <v>0.003717090781415357</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C54" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D54">
         <v>18.19229125976562</v>
@@ -3514,25 +3838,31 @@
       <c r="P54">
         <v>0.01644334449574416</v>
       </c>
-    </row>
-    <row r="55" spans="1:16">
+      <c r="Q54">
+        <v>0.0033741366746208</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B55" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D55">
-        <v>18.82110023498535</v>
+        <v>18.83832740783691</v>
       </c>
       <c r="E55">
         <v>525702980</v>
       </c>
       <c r="F55">
-        <v>9894308480.4105</v>
+        <v>9903364856.515541</v>
       </c>
       <c r="G55">
         <v>175454</v>
@@ -3544,13 +3874,13 @@
         <v>13944618</v>
       </c>
       <c r="J55">
-        <v>9894305922.4105</v>
+        <v>9903362298.515541</v>
       </c>
       <c r="K55">
         <v>0.0125845104668894</v>
       </c>
       <c r="L55">
-        <v>1.773282546303713E-05</v>
+        <v>1.771660923950037E-05</v>
       </c>
       <c r="M55">
         <v>0.008087277830056012</v>
@@ -3564,16 +3894,22 @@
       <c r="P55">
         <v>0.005796203125634427</v>
       </c>
-    </row>
-    <row r="56" spans="1:16">
+      <c r="Q55">
+        <v>0.003413558327204285</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B56" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C56" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D56">
         <v>22.3496208190918</v>
@@ -3614,16 +3950,22 @@
       <c r="P56">
         <v>0.01309694022797001</v>
       </c>
-    </row>
-    <row r="57" spans="1:16">
+      <c r="Q56">
+        <v>0.05612824860365528</v>
+      </c>
+      <c r="R56">
+        <v>0.5008187479934583</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
       <c r="A57" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C57" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D57">
         <v>24.0185546875</v>
@@ -3664,25 +4006,31 @@
       <c r="P57">
         <v>0.01513939661763879</v>
       </c>
-    </row>
-    <row r="58" spans="1:16">
+      <c r="Q57">
+        <v>0.05608669097282939</v>
+      </c>
+      <c r="R57">
+        <v>0.504385596911931</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
       <c r="A58" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C58" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D58">
-        <v>27.60636711120605</v>
+        <v>28.12404251098633</v>
       </c>
       <c r="E58">
         <v>2242084127</v>
       </c>
       <c r="F58">
-        <v>61895797504.16994</v>
+        <v>63056469300.95567</v>
       </c>
       <c r="G58">
         <v>1893004</v>
@@ -3694,13 +4042,13 @@
         <v>24469270</v>
       </c>
       <c r="J58">
-        <v>61927076525.16994</v>
+        <v>63087748321.95567</v>
       </c>
       <c r="K58">
         <v>0.03395626961909918</v>
       </c>
       <c r="L58">
-        <v>3.05682765313586E-05</v>
+        <v>3.000588942149962E-05</v>
       </c>
       <c r="M58">
         <v>0.04682105350915659</v>
@@ -3714,16 +4062,22 @@
       <c r="P58">
         <v>0.01784188999195798</v>
       </c>
-    </row>
-    <row r="59" spans="1:16">
+      <c r="Q58">
+        <v>0.05929791835765975</v>
+      </c>
+      <c r="R58">
+        <v>0.4948310429266706</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C59" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D59">
         <v>14.25649738311768</v>
@@ -3764,16 +4118,22 @@
       <c r="P59">
         <v>0.001438469468485531</v>
       </c>
-    </row>
-    <row r="60" spans="1:16">
+      <c r="Q59">
+        <v>0.4128886864376304</v>
+      </c>
+      <c r="R59">
+        <v>0.3825849296348685</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C60" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D60">
         <v>10.0212230682373</v>
@@ -3814,25 +4174,31 @@
       <c r="P60">
         <v>0.002790760992875618</v>
       </c>
-    </row>
-    <row r="61" spans="1:16">
+      <c r="Q60">
+        <v>0.4054771520624404</v>
+      </c>
+      <c r="R60">
+        <v>0.4023233652493534</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
       <c r="A61" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C61" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D61">
-        <v>7.239703178405762</v>
+        <v>7.869664192199707</v>
       </c>
       <c r="E61">
         <v>1352090</v>
       </c>
       <c r="F61">
-        <v>9788730.270490646</v>
+        <v>10640494.2576313</v>
       </c>
       <c r="G61">
         <v>956000</v>
@@ -3844,13 +4210,13 @@
         <v>4995000</v>
       </c>
       <c r="J61">
-        <v>22374730.27049065</v>
+        <v>23226494.2576313</v>
       </c>
       <c r="K61">
         <v>0.05437688413628348</v>
       </c>
       <c r="L61">
-        <v>0.0427267720523469</v>
+        <v>0.04115989220740433</v>
       </c>
       <c r="M61">
         <v>0.03123123123123123</v>
@@ -3864,16 +4230,22 @@
       <c r="P61">
         <v>0.003552074320324241</v>
       </c>
-    </row>
-    <row r="62" spans="1:16">
+      <c r="Q61">
+        <v>0.4226740744114031</v>
+      </c>
+      <c r="R61">
+        <v>0.3783869939432579</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
       <c r="A62" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B62" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C62" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D62">
         <v>11.11190032958984</v>
@@ -3914,16 +4286,22 @@
       <c r="P62">
         <v>0.0276324337202621</v>
       </c>
-    </row>
-    <row r="63" spans="1:16">
+      <c r="Q62">
+        <v>0.07964097960036146</v>
+      </c>
+      <c r="R62">
+        <v>0.01420682071729523</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
       <c r="A63" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C63" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D63">
         <v>10.15106296539307</v>
@@ -3964,25 +4342,31 @@
       <c r="P63">
         <v>0.01665733218662807</v>
       </c>
-    </row>
-    <row r="64" spans="1:16">
+      <c r="Q63">
+        <v>0.07115965703416588</v>
+      </c>
+      <c r="R63">
+        <v>0.01266911763412746</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
       <c r="A64" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D64">
-        <v>11.63680076599121</v>
+        <v>11.49445533752441</v>
       </c>
       <c r="E64">
         <v>15728175</v>
       </c>
       <c r="F64">
-        <v>183025638.8876438</v>
+        <v>180786805.0782681</v>
       </c>
       <c r="G64">
         <v>4436736</v>
@@ -3994,13 +4378,13 @@
         <v>98140388</v>
       </c>
       <c r="J64">
-        <v>179533722.8876438</v>
+        <v>177294889.0782681</v>
       </c>
       <c r="K64">
         <v>0.04687593900089587</v>
       </c>
       <c r="L64">
-        <v>0.02471254942324461</v>
+        <v>0.02502461307861713</v>
       </c>
       <c r="M64">
         <v>0.03525839942674773</v>
@@ -4014,16 +4398,22 @@
       <c r="P64">
         <v>0.02333267067483131</v>
       </c>
-    </row>
-    <row r="65" spans="1:16">
+      <c r="Q64">
+        <v>0.07457965430534119</v>
+      </c>
+      <c r="R64">
+        <v>0.01216853819256169</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C65" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D65">
         <v>24.1400032043457</v>
@@ -4064,25 +4454,31 @@
       <c r="P65">
         <v>0.009981850110889815</v>
       </c>
-    </row>
-    <row r="66" spans="1:16">
+      <c r="Q65">
+        <v>0.04316206595012919</v>
+      </c>
+      <c r="R65">
+        <v>0.2481070889498751</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C66" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D66">
-        <v>20.13249778747559</v>
+        <v>20.13249969482422</v>
       </c>
       <c r="E66">
         <v>586242289</v>
       </c>
       <c r="F66">
-        <v>11802521586.21712</v>
+        <v>11802522704.38555</v>
       </c>
       <c r="G66">
         <v>147573</v>
@@ -4094,13 +4490,13 @@
         <v>5339617</v>
       </c>
       <c r="J66">
-        <v>11805154221.21712</v>
+        <v>11805155339.38555</v>
       </c>
       <c r="K66">
         <v>0.01851082981320711</v>
       </c>
       <c r="L66">
-        <v>1.25007261433968E-05</v>
+        <v>1.250072495934484E-05</v>
       </c>
       <c r="M66">
         <v>0.01742952724886448</v>
@@ -4114,25 +4510,31 @@
       <c r="P66">
         <v>0.009426138602228842</v>
       </c>
-    </row>
-    <row r="67" spans="1:16">
+      <c r="Q66">
+        <v>0.04266926222161002</v>
+      </c>
+      <c r="R66">
+        <v>0.2700580049811157</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B67" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C67" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D67">
-        <v>19.98336982727051</v>
+        <v>20.0672550201416</v>
       </c>
       <c r="E67">
         <v>586242289</v>
       </c>
       <c r="F67">
-        <v>11715096469.4726</v>
+        <v>11764273516.95455</v>
       </c>
       <c r="G67">
         <v>151093</v>
@@ -4144,13 +4546,13 @@
         <v>5259473</v>
       </c>
       <c r="J67">
-        <v>11718071330.4726</v>
+        <v>11767248377.95455</v>
       </c>
       <c r="K67">
         <v>0.01834914639119569</v>
       </c>
       <c r="L67">
-        <v>1.289401606620074E-05</v>
+        <v>1.28401300921859E-05</v>
       </c>
       <c r="M67">
         <v>0.01630334446055717</v>
@@ -4164,16 +4566,22 @@
       <c r="P67">
         <v>0.00845598974240231</v>
       </c>
-    </row>
-    <row r="68" spans="1:16">
+      <c r="Q67">
+        <v>0.04368305111856689</v>
+      </c>
+      <c r="R67">
+        <v>0.297872191453067</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18">
       <c r="A68" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B68" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C68" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E68">
         <v>734633</v>
@@ -4202,16 +4610,22 @@
       <c r="P68">
         <v>0.002932913177016589</v>
       </c>
-    </row>
-    <row r="69" spans="1:16">
+      <c r="Q68">
+        <v>0.06003023424919565</v>
+      </c>
+      <c r="R68">
+        <v>0.3227119265086548</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18">
       <c r="A69" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C69" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E69">
         <v>734633</v>
@@ -4240,16 +4654,22 @@
       <c r="P69">
         <v>0.009471888752162804</v>
       </c>
-    </row>
-    <row r="70" spans="1:16">
+      <c r="Q69">
+        <v>0.1010498701748989</v>
+      </c>
+      <c r="R69">
+        <v>0.3209667970268883</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
       <c r="A70" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B70" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C70" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E70">
         <v>734633</v>
@@ -4278,25 +4698,31 @@
       <c r="P70">
         <v>0.01723451024471329</v>
       </c>
-    </row>
-    <row r="71" spans="1:16">
+      <c r="Q70">
+        <v>0.1190875630952599</v>
+      </c>
+      <c r="R70">
+        <v>0.2982440837693751</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
       <c r="A71" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C71" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D71">
-        <v>23.27281379699707</v>
+        <v>23.27281188964844</v>
       </c>
       <c r="E71">
         <v>581282851</v>
       </c>
       <c r="F71">
-        <v>13528087554.71059</v>
+        <v>13528086446.00154</v>
       </c>
       <c r="G71">
         <v>338647</v>
@@ -4308,13 +4734,13 @@
         <v>7055968</v>
       </c>
       <c r="J71">
-        <v>13531116678.71059</v>
+        <v>13531115570.00154</v>
       </c>
       <c r="K71">
         <v>0.03357896982992322</v>
       </c>
       <c r="L71">
-        <v>2.502727661293586E-05</v>
+        <v>2.502727866361439E-05</v>
       </c>
       <c r="M71">
         <v>0.03337189170925945</v>
@@ -4328,25 +4754,31 @@
       <c r="P71">
         <v>0.02093152769635502</v>
       </c>
-    </row>
-    <row r="72" spans="1:16">
+      <c r="Q71">
+        <v>0.0307928692480656</v>
+      </c>
+      <c r="R71">
+        <v>0.2718628287176816</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
       <c r="A72" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C72" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D72">
-        <v>20.83856010437012</v>
+        <v>20.83856201171875</v>
       </c>
       <c r="E72">
         <v>577725951</v>
       </c>
       <c r="F72">
-        <v>12038976953.76789</v>
+        <v>12038978055.69269</v>
       </c>
       <c r="G72">
         <v>352812</v>
@@ -4358,13 +4790,13 @@
         <v>7133044</v>
       </c>
       <c r="J72">
-        <v>12041971794.76789</v>
+        <v>12041972896.69269</v>
       </c>
       <c r="K72">
         <v>0.03483570360445443</v>
       </c>
       <c r="L72">
-        <v>2.929852403020021E-05</v>
+        <v>2.92985213491802E-05</v>
       </c>
       <c r="M72">
         <v>0.03956347388295937</v>
@@ -4378,25 +4810,31 @@
       <c r="P72">
         <v>0.02485429779131525</v>
       </c>
-    </row>
-    <row r="73" spans="1:16">
+      <c r="Q72">
+        <v>0.03089745514881992</v>
+      </c>
+      <c r="R72">
+        <v>0.2663342579304496</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
       <c r="A73" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C73" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D73">
-        <v>23.71379852294922</v>
+        <v>23.61210250854492</v>
       </c>
       <c r="E73">
         <v>577763701</v>
       </c>
       <c r="F73">
-        <v>13700971999.38747</v>
+        <v>13642215733.7283</v>
       </c>
       <c r="G73">
         <v>350779</v>
@@ -4408,13 +4846,13 @@
         <v>7309314</v>
       </c>
       <c r="J73">
-        <v>13704460379.38747</v>
+        <v>13645704113.7283</v>
       </c>
       <c r="K73">
         <v>0.03248647350073081</v>
       </c>
       <c r="L73">
-        <v>2.559597315685612E-05</v>
+        <v>2.570618541018325E-05</v>
       </c>
       <c r="M73">
         <v>0.03825365827764411</v>
@@ -4428,25 +4866,31 @@
       <c r="P73">
         <v>0.02314791166857311</v>
       </c>
-    </row>
-    <row r="74" spans="1:16">
+      <c r="Q73">
+        <v>0.02761634079903874</v>
+      </c>
+      <c r="R73">
+        <v>0.2911808069233787</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
       <c r="A74" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B74" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C74" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D74">
-        <v>29.63345718383789</v>
+        <v>29.63345909118652</v>
       </c>
       <c r="E74">
         <v>1033497</v>
       </c>
       <c r="F74">
-        <v>30626089.09912491</v>
+        <v>30626091.070364</v>
       </c>
       <c r="G74">
         <v>673100</v>
@@ -4458,13 +4902,13 @@
         <v>7056881</v>
       </c>
       <c r="J74">
-        <v>38591891.09912491</v>
+        <v>38591893.070364</v>
       </c>
       <c r="K74">
         <v>0.04480557833777096</v>
       </c>
       <c r="L74">
-        <v>0.01744148785741321</v>
+        <v>0.01744148696651774</v>
       </c>
       <c r="M74">
         <v>0.05300174397159312</v>
@@ -4478,16 +4922,22 @@
       <c r="P74">
         <v>0.02166235323511999</v>
       </c>
-    </row>
-    <row r="75" spans="1:16">
+      <c r="Q74">
+        <v>0.02642569984331257</v>
+      </c>
+      <c r="R74">
+        <v>0.5012695886801409</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
       <c r="A75" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B75" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C75" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D75">
         <v>29.18017196655273</v>
@@ -4528,25 +4978,31 @@
       <c r="P75">
         <v>0.02289797629530454</v>
       </c>
-    </row>
-    <row r="76" spans="1:16">
+      <c r="Q75">
+        <v>0.02962362742581611</v>
+      </c>
+      <c r="R75">
+        <v>0.5122987043134852</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
       <c r="A76" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B76" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C76" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D76">
-        <v>29.73213005065918</v>
+        <v>29.64529991149902</v>
       </c>
       <c r="E76">
         <v>1033497</v>
       </c>
       <c r="F76">
-        <v>30728067.21096611</v>
+        <v>30638328.52263451</v>
       </c>
       <c r="G76">
         <v>627571</v>
@@ -4558,13 +5014,13 @@
         <v>6960480</v>
       </c>
       <c r="J76">
-        <v>38803860.21096611</v>
+        <v>38714121.52263451</v>
       </c>
       <c r="K76">
         <v>0.04173713791974913</v>
       </c>
       <c r="L76">
-        <v>0.01617290126776217</v>
+        <v>0.01621038978330131</v>
       </c>
       <c r="M76">
         <v>0.05880082982782796</v>
@@ -4578,16 +5034,22 @@
       <c r="P76">
         <v>0.022818415075691</v>
       </c>
-    </row>
-    <row r="77" spans="1:16">
+      <c r="Q76">
+        <v>0.03523289243295144</v>
+      </c>
+      <c r="R76">
+        <v>0.4958556523750092</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
       <c r="A77" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B77" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C77" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D77">
         <v>7.789999961853027</v>
@@ -4628,16 +5090,22 @@
       <c r="P77">
         <v>-0.01061888187593911</v>
       </c>
-    </row>
-    <row r="78" spans="1:16">
+      <c r="Q77">
+        <v>0.04583833964615895</v>
+      </c>
+      <c r="R77">
+        <v>0.2836337664625003</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
       <c r="A78" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B78" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C78" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D78">
         <v>6.679999828338623</v>
@@ -4678,25 +5146,31 @@
       <c r="P78">
         <v>-0.004489851178991124</v>
       </c>
-    </row>
-    <row r="79" spans="1:16">
+      <c r="Q78">
+        <v>0.0532375891174059</v>
+      </c>
+      <c r="R78">
+        <v>0.2649681270479403</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18">
       <c r="A79" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C79" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D79">
-        <v>7.239999771118164</v>
+        <v>7.340000152587891</v>
       </c>
       <c r="E79">
         <v>562826</v>
       </c>
       <c r="F79">
-        <v>4074860.111179352</v>
+        <v>4131142.925880432</v>
       </c>
       <c r="G79">
         <v>88376</v>
@@ -4708,13 +5182,13 @@
         <v>6569833</v>
       </c>
       <c r="J79">
-        <v>8092083.111179352</v>
+        <v>8148365.925880432</v>
       </c>
       <c r="K79">
         <v>0.008347551954008743</v>
       </c>
       <c r="L79">
-        <v>0.01092129168543846</v>
+        <v>0.01084585557446611</v>
       </c>
       <c r="M79">
         <v>-0.001936426694559816</v>
@@ -4728,25 +5202,31 @@
       <c r="P79">
         <v>-0.0008033404616486072</v>
       </c>
-    </row>
-    <row r="80" spans="1:16">
+      <c r="Q79">
+        <v>0.05906093149858673</v>
+      </c>
+      <c r="R79">
+        <v>0.2617916197230503</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18">
       <c r="A80" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C80" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D80">
-        <v>16.32155227661133</v>
+        <v>16.3215503692627</v>
       </c>
       <c r="E80">
         <v>291387</v>
       </c>
       <c r="F80">
-        <v>4755888.153224945</v>
+        <v>4755887.597448349</v>
       </c>
       <c r="G80">
         <v>257586</v>
@@ -4758,19 +5238,19 @@
         <v>3197081</v>
       </c>
       <c r="J80">
-        <v>8246522.153224945</v>
+        <v>8246521.597448349</v>
       </c>
       <c r="K80">
         <v>0.03851629442941273</v>
       </c>
       <c r="L80">
-        <v>0.03123571309382423</v>
+        <v>0.03123571519896372</v>
       </c>
       <c r="M80">
         <v>0.04707168820558504</v>
       </c>
       <c r="N80" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O80">
         <v>13.55668398127227</v>
@@ -4778,16 +5258,22 @@
       <c r="P80">
         <v>0.02240561894308938</v>
       </c>
-    </row>
-    <row r="81" spans="1:16">
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>0.5198993316368673</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18">
       <c r="A81" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C81" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D81">
         <v>9.549833297729492</v>
@@ -4820,7 +5306,7 @@
         <v>0.007744059424686102</v>
       </c>
       <c r="N81" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O81">
         <v>23.75161073244185</v>
@@ -4828,25 +5314,31 @@
       <c r="P81">
         <v>0.003617227019528002</v>
       </c>
-    </row>
-    <row r="82" spans="1:16">
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81">
+        <v>0.5298401535534198</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18">
       <c r="A82" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C82" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D82">
-        <v>8.43064022064209</v>
+        <v>8.504030227661133</v>
       </c>
       <c r="E82">
         <v>284871</v>
       </c>
       <c r="F82">
-        <v>2401644.910294533</v>
+        <v>2422551.594984055</v>
       </c>
       <c r="G82">
         <v>243395</v>
@@ -4858,19 +5350,19 @@
         <v>3217697</v>
       </c>
       <c r="J82">
-        <v>5980612.910294533</v>
+        <v>6001519.594984055</v>
       </c>
       <c r="K82">
         <v>0.03581094551519017</v>
       </c>
       <c r="L82">
-        <v>0.04069733381022536</v>
+        <v>0.04055556199523608</v>
       </c>
       <c r="M82">
         <v>0.04721171695159613</v>
       </c>
       <c r="N82" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O82">
         <v>14.71611988742579</v>
@@ -4878,16 +5370,22 @@
       <c r="P82">
         <v>0.02227613592705666</v>
       </c>
-    </row>
-    <row r="83" spans="1:16">
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>0.5252304407628667</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18">
       <c r="A83" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C83" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D83">
         <v>4.181328773498535</v>
@@ -4928,16 +5426,22 @@
       <c r="P83">
         <v>0.01898319280183492</v>
       </c>
-    </row>
-    <row r="84" spans="1:16">
+      <c r="Q83">
+        <v>0.1033295831123627</v>
+      </c>
+      <c r="R83">
+        <v>0.2831596251893044</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18">
       <c r="A84" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C84" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D84">
         <v>4.242453575134277</v>
@@ -4978,25 +5482,31 @@
       <c r="P84">
         <v>0.05243610471331235</v>
       </c>
-    </row>
-    <row r="85" spans="1:16">
+      <c r="Q84">
+        <v>0.111426992098175</v>
+      </c>
+      <c r="R84">
+        <v>0.3095758550744571</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18">
       <c r="A85" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C85" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D85">
-        <v>5.640256404876709</v>
+        <v>5.648430824279785</v>
       </c>
       <c r="E85">
         <v>5432044538</v>
       </c>
       <c r="F85">
-        <v>30638123997.03004</v>
+        <v>30682527807.29984</v>
       </c>
       <c r="G85">
         <v>791055</v>
@@ -5008,13 +5518,13 @@
         <v>8945330</v>
       </c>
       <c r="J85">
-        <v>30641031878.03004</v>
+        <v>30685435688.29984</v>
       </c>
       <c r="K85">
         <v>0.06673761228075667</v>
       </c>
       <c r="L85">
-        <v>2.581685248554554E-05</v>
+        <v>2.577949383008514E-05</v>
       </c>
       <c r="M85">
         <v>0.04989273732774532</v>
@@ -5028,16 +5538,22 @@
       <c r="P85">
         <v>0.01582414379712511</v>
       </c>
-    </row>
-    <row r="86" spans="1:16">
+      <c r="Q85">
+        <v>0.1023460352330754</v>
+      </c>
+      <c r="R85">
+        <v>0.3098951999313577</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18">
       <c r="A86" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C86" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D86">
         <v>11.16652870178223</v>
@@ -5078,25 +5594,31 @@
       <c r="P86">
         <v>0.01993374472258515</v>
       </c>
-    </row>
-    <row r="87" spans="1:16">
+      <c r="Q86">
+        <v>0.04830841430687433</v>
+      </c>
+      <c r="R86">
+        <v>0.3091489045480652</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18">
       <c r="A87" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C87" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D87">
-        <v>9.614731788635254</v>
+        <v>9.614730834960938</v>
       </c>
       <c r="E87">
         <v>5459590287</v>
       </c>
       <c r="F87">
-        <v>52492496285.34317</v>
+        <v>52492491078.67213</v>
       </c>
       <c r="G87">
         <v>1835985</v>
@@ -5108,13 +5630,13 @@
         <v>19117069</v>
       </c>
       <c r="J87">
-        <v>52503762031.34317</v>
+        <v>52503756824.67213</v>
       </c>
       <c r="K87">
         <v>0.06042840335893827</v>
       </c>
       <c r="L87">
-        <v>3.496863708364311E-05</v>
+        <v>3.496864055139858E-05</v>
       </c>
       <c r="M87">
         <v>0.0650754046030801</v>
@@ -5128,25 +5650,31 @@
       <c r="P87">
         <v>0.02701155828003094</v>
       </c>
-    </row>
-    <row r="88" spans="1:16">
+      <c r="Q87">
+        <v>0.05558844167220139</v>
+      </c>
+      <c r="R87">
+        <v>0.2924071733417619</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18">
       <c r="A88" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C88" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D88">
-        <v>10.14227485656738</v>
+        <v>10.16121292114258</v>
       </c>
       <c r="E88">
         <v>5394040963</v>
       </c>
       <c r="F88">
-        <v>54707846034.32941</v>
+        <v>54809998730.40796</v>
       </c>
       <c r="G88">
         <v>1602136</v>
@@ -5158,13 +5686,13 @@
         <v>19145192</v>
       </c>
       <c r="J88">
-        <v>54719975070.32941</v>
+        <v>54822127766.40796</v>
       </c>
       <c r="K88">
         <v>0.05122863464447468</v>
       </c>
       <c r="L88">
-        <v>2.927881450861113E-05</v>
+        <v>2.922425789138565E-05</v>
       </c>
       <c r="M88">
         <v>0.062913498073041</v>
@@ -5178,16 +5706,22 @@
       <c r="P88">
         <v>0.02622904404578613</v>
       </c>
-    </row>
-    <row r="89" spans="1:16">
+      <c r="Q88">
+        <v>0.05585316869253521</v>
+      </c>
+      <c r="R88">
+        <v>0.302711931388402</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18">
       <c r="A89" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B89" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C89" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D89">
         <v>48.7400016784668</v>
@@ -5220,7 +5754,7 @@
         <v>0.06790835337572816</v>
       </c>
       <c r="N89" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -5228,16 +5762,22 @@
       <c r="P89">
         <v>0.06504689142323535</v>
       </c>
-    </row>
-    <row r="90" spans="1:16">
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18">
       <c r="A90" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C90" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D90">
         <v>43.7599983215332</v>
@@ -5270,7 +5810,7 @@
         <v>0.079924940824962</v>
       </c>
       <c r="N90" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -5278,25 +5818,31 @@
       <c r="P90">
         <v>0.07704700244297134</v>
       </c>
-    </row>
-    <row r="91" spans="1:16">
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18">
       <c r="A91" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C91" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D91">
-        <v>43.33000183105469</v>
+        <v>43.58000183105469</v>
       </c>
       <c r="E91">
         <v>834325892</v>
       </c>
       <c r="F91">
-        <v>36151342428.05634</v>
+        <v>36359923901.05634</v>
       </c>
       <c r="G91">
         <v>904921</v>
@@ -5308,19 +5854,19 @@
         <v>18191409</v>
       </c>
       <c r="J91">
-        <v>36151326075.05634</v>
+        <v>36359907548.05634</v>
       </c>
       <c r="K91">
         <v>0.04978917258906933</v>
       </c>
       <c r="L91">
-        <v>2.503147458882225E-05</v>
+        <v>2.488787956360944E-05</v>
       </c>
       <c r="M91">
         <v>0.04876747040319966</v>
       </c>
       <c r="N91" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -5328,25 +5874,31 @@
       <c r="P91">
         <v>0.04705346784157175</v>
       </c>
-    </row>
-    <row r="92" spans="1:16">
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18">
       <c r="A92" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B92" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C92" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D92">
-        <v>60.63898849487305</v>
+        <v>60.63898468017578</v>
       </c>
       <c r="E92">
         <v>1283468259</v>
       </c>
       <c r="F92">
-        <v>77828216991.03574</v>
+        <v>77828212094.99289</v>
       </c>
       <c r="G92">
         <v>2870166</v>
@@ -5358,13 +5910,13 @@
         <v>44603775</v>
       </c>
       <c r="J92">
-        <v>77844352319.03574</v>
+        <v>77844347422.99289</v>
       </c>
       <c r="K92">
         <v>0.04725400702740045</v>
       </c>
       <c r="L92">
-        <v>3.687057460812275E-05</v>
+        <v>3.687057692710825E-05</v>
       </c>
       <c r="M92">
         <v>0.004829008307032309</v>
@@ -5378,16 +5930,22 @@
       <c r="P92">
         <v>0.001551769802638313</v>
       </c>
-    </row>
-    <row r="93" spans="1:16">
+      <c r="Q92">
+        <v>0.05628148875984514</v>
+      </c>
+      <c r="R92">
+        <v>0.1385326223773531</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18">
       <c r="A93" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B93" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C93" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D93">
         <v>54.032958984375</v>
@@ -5428,25 +5986,31 @@
       <c r="P93">
         <v>-0.02538680677616532</v>
       </c>
-    </row>
-    <row r="94" spans="1:16">
+      <c r="Q93">
+        <v>0.06831764224893183</v>
+      </c>
+      <c r="R93">
+        <v>0.1462343737344087</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18">
       <c r="A94" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B94" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D94">
-        <v>51.59716415405273</v>
+        <v>51.54029846191406</v>
       </c>
       <c r="E94">
         <v>1239241828</v>
       </c>
       <c r="F94">
-        <v>63941364025.88438</v>
+        <v>63870893681.60797</v>
       </c>
       <c r="G94">
         <v>3942154</v>
@@ -5458,13 +6022,13 @@
         <v>41470752</v>
       </c>
       <c r="J94">
-        <v>63961669826.88438</v>
+        <v>63891199482.60797</v>
       </c>
       <c r="K94">
         <v>0.06381311045308727</v>
       </c>
       <c r="L94">
-        <v>6.163306884685229E-05</v>
+        <v>6.170104853130995E-05</v>
       </c>
       <c r="M94">
         <v>0.07774795113433197</v>
@@ -5478,25 +6042,31 @@
       <c r="P94">
         <v>0.02153381340915211</v>
       </c>
-    </row>
-    <row r="95" spans="1:16">
+      <c r="Q94">
+        <v>0.08234687741419365</v>
+      </c>
+      <c r="R94">
+        <v>0.1524581815485578</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18">
       <c r="A95" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B95" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D95">
-        <v>56.83309936523438</v>
+        <v>56.83310317993164</v>
       </c>
       <c r="E95">
         <v>110989206</v>
       </c>
       <c r="F95">
-        <v>6307860573.066467</v>
+        <v>6307860996.456688</v>
       </c>
       <c r="G95">
         <v>118388</v>
@@ -5508,13 +6078,13 @@
         <v>2940189</v>
       </c>
       <c r="J95">
-        <v>6308544179.066467</v>
+        <v>6308544602.456688</v>
       </c>
       <c r="K95">
         <v>0.03266961845247868</v>
       </c>
       <c r="L95">
-        <v>1.876629482802781E-05</v>
+        <v>1.876629356855099E-05</v>
       </c>
       <c r="M95">
         <v>0.02486234728447729</v>
@@ -5528,25 +6098,31 @@
       <c r="P95">
         <v>0.0145023223554787</v>
       </c>
-    </row>
-    <row r="96" spans="1:16">
+      <c r="Q95">
+        <v>0.175988756831566</v>
+      </c>
+      <c r="R95">
+        <v>0.1359589744973388</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18">
       <c r="A96" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B96" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C96" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D96">
-        <v>45.40812301635742</v>
+        <v>45.40811920166016</v>
       </c>
       <c r="E96">
         <v>110989206</v>
       </c>
       <c r="F96">
-        <v>5039811519.535835</v>
+        <v>5039811096.145615</v>
       </c>
       <c r="G96">
         <v>136069</v>
@@ -5558,13 +6134,13 @@
         <v>3069791</v>
       </c>
       <c r="J96">
-        <v>5040574378.535835</v>
+        <v>5040573955.145615</v>
       </c>
       <c r="K96">
         <v>0.03550258959205772</v>
       </c>
       <c r="L96">
-        <v>2.699474103177994E-05</v>
+        <v>2.699474329924184E-05</v>
       </c>
       <c r="M96">
         <v>0.04215857040430439</v>
@@ -5578,25 +6154,31 @@
       <c r="P96">
         <v>0.02439251943638123</v>
       </c>
-    </row>
-    <row r="97" spans="1:16">
+      <c r="Q96">
+        <v>0.2067766338594587</v>
+      </c>
+      <c r="R96">
+        <v>0.1447211959040591</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18">
       <c r="A97" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C97" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D97">
-        <v>37.66933441162109</v>
+        <v>38.29462432861328</v>
       </c>
       <c r="E97">
         <v>206467158</v>
       </c>
       <c r="F97">
-        <v>7777480419.719009</v>
+        <v>7906582251.806442</v>
       </c>
       <c r="G97">
         <v>318428</v>
@@ -5608,13 +6190,13 @@
         <v>7865406</v>
       </c>
       <c r="J97">
-        <v>7778318761.719009</v>
+        <v>7907420593.806442</v>
       </c>
       <c r="K97">
         <v>0.0365851584857466</v>
       </c>
       <c r="L97">
-        <v>4.093789541862738E-05</v>
+        <v>4.026951598469564E-05</v>
       </c>
       <c r="M97">
         <v>0.02624950320428469</v>
@@ -5628,25 +6210,31 @@
       <c r="P97">
         <v>0.0195692180653693</v>
       </c>
-    </row>
-    <row r="98" spans="1:16">
+      <c r="Q97">
+        <v>0.1186409495908969</v>
+      </c>
+      <c r="R97">
+        <v>0.08028210505084359</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18">
       <c r="A98" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B98" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C98" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D98">
-        <v>6.543917179107666</v>
+        <v>6.543916702270508</v>
       </c>
       <c r="E98">
         <v>173260455</v>
       </c>
       <c r="F98">
-        <v>1133802067.934511</v>
+        <v>1133801985.317488</v>
       </c>
       <c r="G98">
         <v>128333</v>
@@ -5658,13 +6246,13 @@
         <v>2105012</v>
       </c>
       <c r="J98">
-        <v>1134666488.934511</v>
+        <v>1134666406.317488</v>
       </c>
       <c r="K98">
         <v>0.043218015021723</v>
       </c>
       <c r="L98">
-        <v>0.0001131019566115052</v>
+        <v>0.0001131019648466542</v>
       </c>
       <c r="M98">
         <v>0.0713934172346761</v>
@@ -5678,25 +6266,31 @@
       <c r="P98">
         <v>0.04194347048140769</v>
       </c>
-    </row>
-    <row r="99" spans="1:16">
+      <c r="Q98">
+        <v>0.002130609071192318</v>
+      </c>
+      <c r="R98">
+        <v>0.3331148952013291</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18">
       <c r="A99" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B99" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C99" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D99">
-        <v>6.789026737213135</v>
+        <v>6.789026260375977</v>
       </c>
       <c r="E99">
         <v>173260455</v>
       </c>
       <c r="F99">
-        <v>1176269861.496713</v>
+        <v>1176269778.87969</v>
       </c>
       <c r="G99">
         <v>138391</v>
@@ -5708,13 +6302,13 @@
         <v>2252491</v>
       </c>
       <c r="J99">
-        <v>1177095337.496713</v>
+        <v>1177095254.87969</v>
       </c>
       <c r="K99">
         <v>0.04496182057832329</v>
       </c>
       <c r="L99">
-        <v>0.0001175699160395208</v>
+        <v>0.0001175699242914243</v>
       </c>
       <c r="M99">
         <v>0.06489215717177116</v>
@@ -5728,25 +6322,31 @@
       <c r="P99">
         <v>0.03872088033187283</v>
       </c>
-    </row>
-    <row r="100" spans="1:16">
+      <c r="Q99">
+        <v>0.001164786725087021</v>
+      </c>
+      <c r="R99">
+        <v>0.3103469194212358</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18">
       <c r="A100" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C100" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D100">
-        <v>8.292414665222168</v>
+        <v>8.402066230773926</v>
       </c>
       <c r="E100">
         <v>173260455</v>
       </c>
       <c r="F100">
-        <v>1436747537.945065</v>
+        <v>1455745818.084025</v>
       </c>
       <c r="G100">
         <v>132566</v>
@@ -5758,13 +6358,13 @@
         <v>2058528</v>
       </c>
       <c r="J100">
-        <v>1437546384.945065</v>
+        <v>1456544665.084025</v>
       </c>
       <c r="K100">
         <v>0.04639433046065007</v>
       </c>
       <c r="L100">
-        <v>9.221685045318791E-05</v>
+        <v>9.101403010689859E-05</v>
       </c>
       <c r="M100">
         <v>0.07795084643007041</v>
@@ -5778,16 +6378,22 @@
       <c r="P100">
         <v>0.03970487586287783</v>
       </c>
-    </row>
-    <row r="101" spans="1:16">
+      <c r="Q100">
+        <v>0.001060271419585898</v>
+      </c>
+      <c r="R100">
+        <v>0.3588485526614669</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18">
       <c r="A101" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C101" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E101">
         <v>1061390989</v>
@@ -5816,16 +6422,22 @@
       <c r="P101">
         <v>0.01128277790388239</v>
       </c>
-    </row>
-    <row r="102" spans="1:16">
+      <c r="Q101">
+        <v>0.07563490803068264</v>
+      </c>
+      <c r="R101">
+        <v>0.4983687147106642</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18">
       <c r="A102" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C102" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E102">
         <v>1062027453</v>
@@ -5854,16 +6466,22 @@
       <c r="P102">
         <v>-0.008603287629395428</v>
       </c>
-    </row>
-    <row r="103" spans="1:16">
+      <c r="Q102">
+        <v>0.07610198619312768</v>
+      </c>
+      <c r="R102">
+        <v>0.5095658624950284</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18">
       <c r="A103" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C103" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E103">
         <v>1060680236</v>
@@ -5892,25 +6510,31 @@
       <c r="P103">
         <v>0.01197664785618538</v>
       </c>
-    </row>
-    <row r="104" spans="1:16">
+      <c r="Q103">
+        <v>0.08129210746734422</v>
+      </c>
+      <c r="R103">
+        <v>0.4972385784313798</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18">
       <c r="A104" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B104" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C104" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D104">
-        <v>7.162896156311035</v>
+        <v>7.162894725799561</v>
       </c>
       <c r="E104">
         <v>2200525</v>
       </c>
       <c r="F104">
-        <v>15762132.06436634</v>
+        <v>15762128.91649008</v>
       </c>
       <c r="G104">
         <v>1173973</v>
@@ -5922,13 +6546,13 @@
         <v>25414552</v>
       </c>
       <c r="J104">
-        <v>15434908.06436634</v>
+        <v>15434904.91649008</v>
       </c>
       <c r="K104">
         <v>0.04679545785027405</v>
       </c>
       <c r="L104">
-        <v>0.07605960431408607</v>
+        <v>0.07605961982608464</v>
       </c>
       <c r="M104">
         <v>0.04534362832758177</v>
@@ -5942,25 +6566,31 @@
       <c r="P104">
         <v>0.03823998408265657</v>
       </c>
-    </row>
-    <row r="105" spans="1:16">
+      <c r="Q104">
+        <v>0.03352159078397496</v>
+      </c>
+      <c r="R104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18">
       <c r="A105" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C105" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D105">
-        <v>7.583364009857178</v>
+        <v>7.58336353302002</v>
       </c>
       <c r="E105">
         <v>2860520</v>
       </c>
       <c r="F105">
-        <v>21692364.41747665</v>
+        <v>21692363.05347443</v>
       </c>
       <c r="G105">
         <v>1683820</v>
@@ -5972,13 +6602,13 @@
         <v>26672836</v>
       </c>
       <c r="J105">
-        <v>21488751.41747665</v>
+        <v>21488750.05347443</v>
       </c>
       <c r="K105">
         <v>0.06361425871851244</v>
       </c>
       <c r="L105">
-        <v>0.07835820552284675</v>
+        <v>0.07835821049664776</v>
       </c>
       <c r="M105">
         <v>0.06328509649292637</v>
@@ -5992,25 +6622,31 @@
       <c r="P105">
         <v>0.05549341013021938</v>
       </c>
-    </row>
-    <row r="106" spans="1:16">
+      <c r="Q105">
+        <v>0.03098793802333494</v>
+      </c>
+      <c r="R105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18">
       <c r="A106" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C106" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D106">
-        <v>9.250566482543945</v>
+        <v>9.185650825500488</v>
       </c>
       <c r="E106">
         <v>2860682</v>
       </c>
       <c r="F106">
-        <v>26462929.02641678</v>
+        <v>26277225.97479439</v>
       </c>
       <c r="G106">
         <v>3280424</v>
@@ -6022,13 +6658,13 @@
         <v>28060032</v>
       </c>
       <c r="J106">
-        <v>26261568.02641678</v>
+        <v>26075864.97479439</v>
       </c>
       <c r="K106">
         <v>0.1177523507851469</v>
       </c>
       <c r="L106">
-        <v>0.1249134856189923</v>
+        <v>0.1258030751106797</v>
       </c>
       <c r="M106">
         <v>0.1168791967165255</v>
@@ -6042,25 +6678,31 @@
       <c r="P106">
         <v>0.1016095226431264</v>
       </c>
-    </row>
-    <row r="107" spans="1:16">
+      <c r="Q106">
+        <v>0.03149456683131622</v>
+      </c>
+      <c r="R106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18">
       <c r="A107" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B107" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C107" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D107">
-        <v>18.41388320922852</v>
+        <v>18.41388130187988</v>
       </c>
       <c r="E107">
         <v>379181</v>
       </c>
       <c r="F107">
-        <v>6982194.649158478</v>
+        <v>6982193.925928116</v>
       </c>
       <c r="G107">
         <v>510575</v>
@@ -6072,13 +6714,13 @@
         <v>7752948</v>
       </c>
       <c r="J107">
-        <v>10844322.64915848</v>
+        <v>10844321.92592812</v>
       </c>
       <c r="K107">
         <v>0.04395795602198384</v>
       </c>
       <c r="L107">
-        <v>0.04708223985198566</v>
+        <v>0.04708224299199806</v>
       </c>
       <c r="M107">
         <v>0.0453440420340753</v>
@@ -6092,25 +6734,31 @@
       <c r="P107">
         <v>0.02487642280507407</v>
       </c>
-    </row>
-    <row r="108" spans="1:16">
+      <c r="Q107">
+        <v>0.1304620660203491</v>
+      </c>
+      <c r="R107">
+        <v>0.3255122558220417</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18">
       <c r="A108" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B108" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C108" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D108">
-        <v>18.66683959960938</v>
+        <v>18.66683769226074</v>
       </c>
       <c r="E108">
         <v>379181</v>
       </c>
       <c r="F108">
-        <v>7078110.906219482</v>
+        <v>7078110.18298912</v>
       </c>
       <c r="G108">
         <v>533470</v>
@@ -6122,13 +6770,13 @@
         <v>7632247</v>
       </c>
       <c r="J108">
-        <v>11790266.90621948</v>
+        <v>11790266.18298912</v>
       </c>
       <c r="K108">
         <v>0.04321553662821928</v>
       </c>
       <c r="L108">
-        <v>0.0452466432052178</v>
+        <v>0.04524664598070612</v>
       </c>
       <c r="M108">
         <v>0.04260514629571082</v>
@@ -6142,25 +6790,31 @@
       <c r="P108">
         <v>0.02273831321830139</v>
       </c>
-    </row>
-    <row r="109" spans="1:16">
+      <c r="Q108">
+        <v>0.1355861423227521</v>
+      </c>
+      <c r="R108">
+        <v>0.3490996397719966</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18">
       <c r="A109" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C109" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D109">
-        <v>20.87222862243652</v>
+        <v>20.53703880310059</v>
       </c>
       <c r="E109">
         <v>379181</v>
       </c>
       <c r="F109">
-        <v>7914352.521284103</v>
+        <v>7787254.910398483</v>
       </c>
       <c r="G109">
         <v>523919</v>
@@ -6172,13 +6826,13 @@
         <v>7866589</v>
       </c>
       <c r="J109">
-        <v>13231298.5212841</v>
+        <v>13104200.91039848</v>
       </c>
       <c r="K109">
         <v>0.03974040346538315</v>
       </c>
       <c r="L109">
-        <v>0.03959694501316061</v>
+        <v>0.03998099568087805</v>
       </c>
       <c r="M109">
         <v>0.04681406388461377</v>
@@ -6192,16 +6846,22 @@
       <c r="P109">
         <v>0.02400343260942453</v>
       </c>
-    </row>
-    <row r="110" spans="1:16">
+      <c r="Q109">
+        <v>0.1317462663919745</v>
+      </c>
+      <c r="R109">
+        <v>0.4015121236344258</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18">
       <c r="A110" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C110" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D110">
         <v>7.626565456390381</v>
@@ -6242,16 +6902,22 @@
       <c r="P110">
         <v>0.008917692906010546</v>
       </c>
-    </row>
-    <row r="111" spans="1:16">
+      <c r="Q110">
+        <v>0.04822937138200047</v>
+      </c>
+      <c r="R110">
+        <v>0.5938126510233028</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18">
       <c r="A111" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B111" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C111" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D111">
         <v>6.914143562316895</v>
@@ -6292,25 +6958,31 @@
       <c r="P111">
         <v>0.006791558053702618</v>
       </c>
-    </row>
-    <row r="112" spans="1:16">
+      <c r="Q111">
+        <v>0.05327838082728975</v>
+      </c>
+      <c r="R111">
+        <v>0.6125288492700471</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18">
       <c r="A112" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C112" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D112">
-        <v>6.037316799163818</v>
+        <v>5.93684720993042</v>
       </c>
       <c r="E112">
         <v>1090678837</v>
       </c>
       <c r="F112">
-        <v>6584773665.112556</v>
+        <v>6475193610.373606</v>
       </c>
       <c r="G112">
         <v>655790</v>
@@ -6322,13 +6994,13 @@
         <v>5199352</v>
       </c>
       <c r="J112">
-        <v>6599295151.112556</v>
+        <v>6489715096.373606</v>
       </c>
       <c r="K112">
         <v>0.03325365788208392</v>
       </c>
       <c r="L112">
-        <v>9.937273375164047E-05</v>
+        <v>0.0001010506609706872</v>
       </c>
       <c r="M112">
         <v>0.03366861870479244</v>
@@ -6342,16 +7014,22 @@
       <c r="P112">
         <v>0.007628858215890913</v>
       </c>
-    </row>
-    <row r="113" spans="1:16">
+      <c r="Q112">
+        <v>0.04953107721979488</v>
+      </c>
+      <c r="R112">
+        <v>0.6408080963559373</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18">
       <c r="A113" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B113" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C113" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D113">
         <v>11.82089805603027</v>
@@ -6384,7 +7062,7 @@
         <v>0.02074845389584705</v>
       </c>
       <c r="N113" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O113">
         <v>1.747394000612689</v>
@@ -6392,16 +7070,22 @@
       <c r="P113">
         <v>0.01881786071096934</v>
       </c>
-    </row>
-    <row r="114" spans="1:16">
+      <c r="Q113">
+        <v>0</v>
+      </c>
+      <c r="R113">
+        <v>0.03131860732486664</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18">
       <c r="A114" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B114" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C114" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D114">
         <v>12.25797367095947</v>
@@ -6434,7 +7118,7 @@
         <v>0.007396268809781208</v>
       </c>
       <c r="N114" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O114">
         <v>9.704229472895797</v>
@@ -6442,25 +7126,31 @@
       <c r="P114">
         <v>0.006531268801624138</v>
       </c>
-    </row>
-    <row r="115" spans="1:16">
+      <c r="Q114">
+        <v>0</v>
+      </c>
+      <c r="R114">
+        <v>0.05945584877634343</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18">
       <c r="A115" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B115" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C115" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D115">
-        <v>10.39046955108643</v>
+        <v>10.37060260772705</v>
       </c>
       <c r="E115">
         <v>1000000</v>
       </c>
       <c r="F115">
-        <v>10390469.55108643</v>
+        <v>10370602.60772705</v>
       </c>
       <c r="G115">
         <v>267373</v>
@@ -6472,19 +7162,19 @@
         <v>12587285</v>
       </c>
       <c r="J115">
-        <v>10623346.55108643</v>
+        <v>10603479.60772705</v>
       </c>
       <c r="K115">
         <v>0.0208556646944087</v>
       </c>
       <c r="L115">
-        <v>0.02516843432662529</v>
+        <v>0.02521559053173053</v>
       </c>
       <c r="M115">
         <v>0.02151615697904671</v>
       </c>
       <c r="N115" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O115">
         <v>3.210686942959835</v>
@@ -6492,16 +7182,22 @@
       <c r="P115">
         <v>0.01899821339771434</v>
       </c>
-    </row>
-    <row r="116" spans="1:16">
+      <c r="Q115">
+        <v>0</v>
+      </c>
+      <c r="R115">
+        <v>0.06021871760691677</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18">
       <c r="A116" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B116" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C116" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D116">
         <v>29.22310829162598</v>
@@ -6539,25 +7235,31 @@
       <c r="P116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:16">
+      <c r="Q116">
+        <v>0.01689140969157309</v>
+      </c>
+      <c r="R116">
+        <v>0.002881279673020394</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18">
       <c r="A117" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B117" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C117" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D117">
-        <v>31.85553550720215</v>
+        <v>32.65024566650391</v>
       </c>
       <c r="E117">
         <v>11433761128</v>
       </c>
       <c r="F117">
-        <v>364228583593.8717</v>
+        <v>373315109721.3228</v>
       </c>
       <c r="G117">
         <v>3256231</v>
@@ -6569,13 +7271,13 @@
         <v>0</v>
       </c>
       <c r="J117">
-        <v>364228850566.8717</v>
+        <v>373315376694.3228</v>
       </c>
       <c r="K117">
         <v>12.1968551126893</v>
       </c>
       <c r="L117">
-        <v>8.940068846638942E-06</v>
+        <v>8.722466855862353E-06</v>
       </c>
       <c r="N117">
         <v>0</v>
@@ -6586,25 +7288,31 @@
       <c r="P117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:16">
+      <c r="Q117">
+        <v>0.02161289071199733</v>
+      </c>
+      <c r="R117">
+        <v>0.003115336003281563</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18">
       <c r="A118" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B118" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C118" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D118">
-        <v>28.24449729919434</v>
+        <v>28.2445011138916</v>
       </c>
       <c r="E118">
         <v>12909287661</v>
       </c>
       <c r="F118">
-        <v>364616340475.6373</v>
+        <v>364616389720.6616</v>
       </c>
       <c r="G118">
         <v>48148000</v>
@@ -6616,13 +7324,13 @@
         <v>407636000</v>
       </c>
       <c r="J118">
-        <v>365180392475.6373</v>
+        <v>365180441720.6616</v>
       </c>
       <c r="K118">
         <v>0.04955088464610039</v>
       </c>
       <c r="L118">
-        <v>0.0001318471664746134</v>
+        <v>0.0001318471486948635</v>
       </c>
       <c r="M118">
         <v>0.0581401053881404</v>
@@ -6636,16 +7344,22 @@
       <c r="P118">
         <v>0.01783803068141277</v>
       </c>
-    </row>
-    <row r="119" spans="1:16">
+      <c r="Q118">
+        <v>0.08683884505901604</v>
+      </c>
+      <c r="R118">
+        <v>0.4295811750821528</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18">
       <c r="A119" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B119" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C119" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D119">
         <v>32.73216247558594</v>
@@ -6686,25 +7400,31 @@
       <c r="P119">
         <v>-0.001867955280935455</v>
       </c>
-    </row>
-    <row r="120" spans="1:16">
+      <c r="Q119">
+        <v>0.08369658669714672</v>
+      </c>
+      <c r="R119">
+        <v>0.4764254004630808</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18">
       <c r="A120" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B120" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C120" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D120">
-        <v>32.6773681640625</v>
+        <v>32.88539505004883</v>
       </c>
       <c r="E120">
         <v>12888732761</v>
       </c>
       <c r="F120">
-        <v>421169865599.4108</v>
+        <v>423851068539.9916</v>
       </c>
       <c r="G120">
         <v>48832000</v>
@@ -6716,13 +7436,13 @@
         <v>393655000</v>
       </c>
       <c r="J120">
-        <v>421842194599.4108</v>
+        <v>424523397539.9916</v>
       </c>
       <c r="K120">
         <v>0.04580931796349664</v>
       </c>
       <c r="L120">
-        <v>0.0001157589274500427</v>
+        <v>0.0001150278177433079</v>
       </c>
       <c r="M120">
         <v>0.08269931793067534</v>
@@ -6736,16 +7456,22 @@
       <c r="P120">
         <v>0.02244725016875947</v>
       </c>
-    </row>
-    <row r="121" spans="1:16">
+      <c r="Q120">
+        <v>0.08397636608979314</v>
+      </c>
+      <c r="R120">
+        <v>0.4791838040556055</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18">
       <c r="A121" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B121" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C121" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D121">
         <v>14.1755485534668</v>
@@ -6786,16 +7512,22 @@
       <c r="P121">
         <v>-0.009310592894771312</v>
       </c>
-    </row>
-    <row r="122" spans="1:16">
+      <c r="Q121">
+        <v>0.06643530164122564</v>
+      </c>
+      <c r="R121">
+        <v>0.4071277749056438</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18">
       <c r="A122" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B122" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D122">
         <v>12.2898588180542</v>
@@ -6836,25 +7568,31 @@
       <c r="P122">
         <v>-0.008297174542956278</v>
       </c>
-    </row>
-    <row r="123" spans="1:16">
+      <c r="Q122">
+        <v>0.07317957656619155</v>
+      </c>
+      <c r="R122">
+        <v>0.450179435094375</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18">
       <c r="A123" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B123" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D123">
-        <v>12.27082061767578</v>
+        <v>12.61352729797363</v>
       </c>
       <c r="E123">
         <v>1326093947</v>
       </c>
       <c r="F123">
-        <v>16272260945.82265</v>
+        <v>16726722200.1621</v>
       </c>
       <c r="G123">
         <v>5546</v>
@@ -6866,13 +7604,13 @@
         <v>13418340</v>
       </c>
       <c r="J123">
-        <v>16299846225.82265</v>
+        <v>16754307480.1621</v>
       </c>
       <c r="K123">
         <v>0.000135256350536855</v>
       </c>
       <c r="L123">
-        <v>3.402486086779075E-07</v>
+        <v>3.310193516841403E-07</v>
       </c>
       <c r="M123">
         <v>-0.06262600291839378</v>
@@ -6886,16 +7624,22 @@
       <c r="P123">
         <v>-0.01329039873204772</v>
       </c>
-    </row>
-    <row r="124" spans="1:16">
+      <c r="Q123">
+        <v>0.08024545366754729</v>
+      </c>
+      <c r="R123">
+        <v>0.4595677310611142</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18">
       <c r="A124" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B124" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D124">
         <v>25.68557167053223</v>
@@ -6928,7 +7672,7 @@
         <v>0.03120241615987707</v>
       </c>
       <c r="N124" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O124">
         <v>0.01869882136473317</v>
@@ -6936,16 +7680,22 @@
       <c r="P124">
         <v>0.03022192212500582</v>
       </c>
-    </row>
-    <row r="125" spans="1:16">
+      <c r="Q124">
+        <v>0</v>
+      </c>
+      <c r="R124">
+        <v>0.0005737257960524219</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18">
       <c r="A125" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B125" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C125" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D125">
         <v>19.48747444152832</v>
@@ -6978,7 +7728,7 @@
         <v>0.03065815390048112</v>
       </c>
       <c r="N125" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O125">
         <v>0.02146526313722699</v>
@@ -6986,25 +7736,31 @@
       <c r="P125">
         <v>0.02978581812391686</v>
       </c>
-    </row>
-    <row r="126" spans="1:16">
+      <c r="Q125">
+        <v>0</v>
+      </c>
+      <c r="R125">
+        <v>0.0005948797490649485</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18">
       <c r="A126" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C126" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D126">
-        <v>19.33918571472168</v>
+        <v>19.45772171020508</v>
       </c>
       <c r="E126">
         <v>1103883766</v>
       </c>
       <c r="F126">
-        <v>21348213158.14037</v>
+        <v>21479063119.24114</v>
       </c>
       <c r="G126">
         <v>653569</v>
@@ -7016,19 +7772,19 @@
         <v>14703834</v>
       </c>
       <c r="J126">
-        <v>21348169924.14037</v>
+        <v>21479019885.24114</v>
       </c>
       <c r="K126">
         <v>0.04457996262090228</v>
       </c>
       <c r="L126">
-        <v>3.061475537820919E-05</v>
+        <v>3.042825061347824E-05</v>
       </c>
       <c r="M126">
         <v>0.04431374837338343</v>
       </c>
       <c r="N126" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O126">
         <v>0.01344004994116918</v>
@@ -7036,16 +7792,22 @@
       <c r="P126">
         <v>0.04306646457388006</v>
       </c>
-    </row>
-    <row r="127" spans="1:16">
+      <c r="Q126">
+        <v>0</v>
+      </c>
+      <c r="R126">
+        <v>0.0005805805329443761</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18">
       <c r="A127" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C127" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D127">
         <v>51.39371109008789</v>
@@ -7086,16 +7848,22 @@
       <c r="P127">
         <v>0.0198165339350077</v>
       </c>
-    </row>
-    <row r="128" spans="1:16">
+      <c r="Q127">
+        <v>0.08412765184469918</v>
+      </c>
+      <c r="R127">
+        <v>0.04669588993948201</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18">
       <c r="A128" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C128" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D128">
         <v>52.56808471679688</v>
@@ -7136,25 +7904,31 @@
       <c r="P128">
         <v>0.03362793109408308</v>
       </c>
-    </row>
-    <row r="129" spans="1:16">
+      <c r="Q128">
+        <v>0.0757504176989111</v>
+      </c>
+      <c r="R128">
+        <v>0.04356282767759406</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18">
       <c r="A129" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B129" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C129" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D129">
-        <v>55.61813354492188</v>
+        <v>56.01221466064453</v>
       </c>
       <c r="E129">
         <v>4269039</v>
       </c>
       <c r="F129">
-        <v>237435981.2104797</v>
+        <v>239118328.8626633</v>
       </c>
       <c r="G129">
         <v>17429000</v>
@@ -7166,13 +7940,13 @@
         <v>208555000</v>
       </c>
       <c r="J129">
-        <v>252269981.2104797</v>
+        <v>253952328.8626633</v>
       </c>
       <c r="K129">
         <v>0.07802085151909897</v>
       </c>
       <c r="L129">
-        <v>0.06908867997836902</v>
+        <v>0.06863099101337856</v>
       </c>
       <c r="M129">
         <v>0.06418450768382442</v>
@@ -7186,16 +7960,22 @@
       <c r="P129">
         <v>0.03034073832303162</v>
       </c>
-    </row>
-    <row r="130" spans="1:16">
+      <c r="Q129">
+        <v>0.08541690749316053</v>
+      </c>
+      <c r="R129">
+        <v>0.04757598217543955</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18">
       <c r="A130" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B130" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C130" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D130">
         <v>16.98406028747559</v>
@@ -7236,25 +8016,31 @@
       <c r="P130">
         <v>0.03677494991712608</v>
       </c>
-    </row>
-    <row r="131" spans="1:16">
+      <c r="Q130">
+        <v>0.02487622892760887</v>
+      </c>
+      <c r="R130">
+        <v>0.01505456057569372</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18">
       <c r="A131" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B131" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C131" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D131">
-        <v>17.11531448364258</v>
+        <v>17.11531639099121</v>
       </c>
       <c r="E131">
         <v>2103651618</v>
       </c>
       <c r="F131">
-        <v>36004659006.09354</v>
+        <v>36004663018.49059</v>
       </c>
       <c r="G131">
         <v>1140156</v>
@@ -7266,13 +8052,13 @@
         <v>55130309</v>
       </c>
       <c r="J131">
-        <v>36006503135.09354</v>
+        <v>36006507147.49059</v>
       </c>
       <c r="K131">
         <v>0.0200117112168794</v>
       </c>
       <c r="L131">
-        <v>3.166527990019539E-05</v>
+        <v>3.166527637156444E-05</v>
       </c>
       <c r="M131">
         <v>0.01558326110597349</v>
@@ -7286,25 +8072,31 @@
       <c r="P131">
         <v>0.01430585672225981</v>
       </c>
-    </row>
-    <row r="132" spans="1:16">
+      <c r="Q131">
+        <v>0.02371853795146746</v>
+      </c>
+      <c r="R131">
+        <v>0.03865645273801103</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18">
       <c r="A132" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B132" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C132" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D132">
-        <v>17.90850448608398</v>
+        <v>17.81474494934082</v>
       </c>
       <c r="E132">
         <v>2085040387</v>
       </c>
       <c r="F132">
-        <v>37339955124.25578</v>
+        <v>37144462703.47988</v>
       </c>
       <c r="G132">
         <v>1475790</v>
@@ -7316,13 +8108,13 @@
         <v>55294999</v>
       </c>
       <c r="J132">
-        <v>37341119883.25578</v>
+        <v>37145627462.47988</v>
       </c>
       <c r="K132">
         <v>0.02613879428955398</v>
       </c>
       <c r="L132">
-        <v>3.952184628136346E-05</v>
+        <v>3.972984442087211E-05</v>
       </c>
       <c r="M132">
         <v>0.02436752010792151</v>
@@ -7336,16 +8128,22 @@
       <c r="P132">
         <v>0.02260863492523515</v>
       </c>
-    </row>
-    <row r="133" spans="1:16">
+      <c r="Q132">
+        <v>0.02826694331692747</v>
+      </c>
+      <c r="R132">
+        <v>0.04003680601103546</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18">
       <c r="A133" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B133" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C133" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D133">
         <v>23.66582107543945</v>
@@ -7378,7 +8176,7 @@
         <v>0.01817776232252093</v>
       </c>
       <c r="N133" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -7386,16 +8184,22 @@
       <c r="P133">
         <v>0.01736852594698789</v>
       </c>
-    </row>
-    <row r="134" spans="1:16">
+      <c r="Q133">
+        <v>0</v>
+      </c>
+      <c r="R133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18">
       <c r="A134" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B134" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C134" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D134">
         <v>19.83210372924805</v>
@@ -7428,7 +8232,7 @@
         <v>0.09703786211367069</v>
       </c>
       <c r="N134" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O134">
         <v>0</v>
@@ -7436,25 +8240,31 @@
       <c r="P134">
         <v>0.09689235316747181</v>
       </c>
-    </row>
-    <row r="135" spans="1:16">
+      <c r="Q134">
+        <v>0</v>
+      </c>
+      <c r="R134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18">
       <c r="A135" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B135" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C135" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D135">
-        <v>25.50518226623535</v>
+        <v>25.6756591796875</v>
       </c>
       <c r="E135">
         <v>234976350</v>
       </c>
       <c r="F135">
-        <v>5993114635.004711</v>
+        <v>6033172677.886963</v>
       </c>
       <c r="G135">
         <v>107100773</v>
@@ -7466,19 +8276,19 @@
         <v>2282183438</v>
       </c>
       <c r="J135">
-        <v>5991367525.004711</v>
+        <v>6031425567.886963</v>
       </c>
       <c r="K135">
         <v>0.04696503545614451</v>
       </c>
       <c r="L135">
-        <v>0.01787584763462091</v>
+        <v>0.01775712421458622</v>
       </c>
       <c r="M135">
         <v>0.04695734979740047</v>
       </c>
       <c r="N135" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -7486,25 +8296,31 @@
       <c r="P135">
         <v>0.04686451354507407</v>
       </c>
-    </row>
-    <row r="136" spans="1:16">
+      <c r="Q135">
+        <v>0</v>
+      </c>
+      <c r="R135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18">
       <c r="A136" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B136" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C136" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D136">
-        <v>19.9079647064209</v>
+        <v>19.90796661376953</v>
       </c>
       <c r="E136">
         <v>1115113</v>
       </c>
       <c r="F136">
-        <v>22199630.24767113</v>
+        <v>22199632.37458038</v>
       </c>
       <c r="G136">
         <v>1565000</v>
@@ -7516,13 +8332,13 @@
         <v>16556000</v>
       </c>
       <c r="J136">
-        <v>32725630.24767113</v>
+        <v>32725632.37458038</v>
       </c>
       <c r="K136">
         <v>0.05778746030573813</v>
       </c>
       <c r="L136">
-        <v>0.04782184447345735</v>
+        <v>0.04782184136541279</v>
       </c>
       <c r="M136">
         <v>0.04765643875332206</v>
@@ -7536,16 +8352,22 @@
       <c r="P136">
         <v>0.01849507735583685</v>
       </c>
-    </row>
-    <row r="137" spans="1:16">
+      <c r="Q136">
+        <v>0.9234646038443507</v>
+      </c>
+      <c r="R136">
+        <v>0.356657290201594</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18">
       <c r="A137" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B137" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C137" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D137">
         <v>17.06504440307617</v>
@@ -7586,25 +8408,31 @@
       <c r="P137">
         <v>0.01970723280447334</v>
       </c>
-    </row>
-    <row r="138" spans="1:16">
+      <c r="Q137">
+        <v>0.9541073782788562</v>
+      </c>
+      <c r="R137">
+        <v>0.4144201482020275</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18">
       <c r="A138" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C138" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D138">
-        <v>19.7378978729248</v>
+        <v>19.92346954345703</v>
       </c>
       <c r="E138">
         <v>1114497</v>
       </c>
       <c r="F138">
-        <v>21997827.96568108</v>
+        <v>22204647.03577423</v>
       </c>
       <c r="G138">
         <v>5660000</v>
@@ -7616,13 +8444,13 @@
         <v>20424000</v>
       </c>
       <c r="J138">
-        <v>31931827.96568108</v>
+        <v>32138647.03577423</v>
       </c>
       <c r="K138">
         <v>0.1864417945846235</v>
       </c>
       <c r="L138">
-        <v>0.1772526147292012</v>
+        <v>0.1761119562282672</v>
       </c>
       <c r="M138">
         <v>0.2056893850372111</v>
@@ -7636,16 +8464,22 @@
       <c r="P138">
         <v>0.08968447120105888</v>
       </c>
-    </row>
-    <row r="139" spans="1:16">
+      <c r="Q138">
+        <v>0.985675248708424</v>
+      </c>
+      <c r="R138">
+        <v>0.3548524828145681</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18">
       <c r="A139" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C139" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D139">
         <v>26.39999961853027</v>
@@ -7686,16 +8520,22 @@
       <c r="P139">
         <v>-0.01710825902794561</v>
       </c>
-    </row>
-    <row r="140" spans="1:16">
+      <c r="Q139">
+        <v>0.1533256165969192</v>
+      </c>
+      <c r="R139">
+        <v>0.1228105880407546</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18">
       <c r="A140" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C140" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D140">
         <v>17.86000061035156</v>
@@ -7736,25 +8576,31 @@
       <c r="P140">
         <v>-0.04549828848473036</v>
       </c>
-    </row>
-    <row r="141" spans="1:16">
+      <c r="Q140">
+        <v>0.1523918578163258</v>
+      </c>
+      <c r="R140">
+        <v>0.1130209158129393</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18">
       <c r="A141" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C141" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D141">
-        <v>19.93000030517578</v>
+        <v>20.30999946594238</v>
       </c>
       <c r="E141">
         <v>797207780</v>
       </c>
       <c r="F141">
-        <v>15888351298.68851</v>
+        <v>16191289586.04511</v>
       </c>
       <c r="G141">
         <v>457000</v>
@@ -7766,13 +8612,13 @@
         <v>-25000</v>
       </c>
       <c r="J141">
-        <v>15892155298.68851</v>
+        <v>16195093586.04511</v>
       </c>
       <c r="K141">
         <v>0.1209314633500926</v>
       </c>
       <c r="L141">
-        <v>2.875632608735668E-05</v>
+        <v>2.821842291753009E-05</v>
       </c>
       <c r="M141">
         <v>23.72</v>
@@ -7786,16 +8632,22 @@
       <c r="P141">
         <v>-0.007432661093215347</v>
       </c>
-    </row>
-    <row r="142" spans="1:16">
+      <c r="Q141">
+        <v>0.1838737575674016</v>
+      </c>
+      <c r="R141">
+        <v>0.1128310542346114</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18">
       <c r="A142" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B142" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C142" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D142">
         <v>15.23028182983398</v>
@@ -7836,16 +8688,22 @@
       <c r="P142">
         <v>0.01267155551884225</v>
       </c>
-    </row>
-    <row r="143" spans="1:16">
+      <c r="Q142">
+        <v>0.1008391828239216</v>
+      </c>
+      <c r="R142">
+        <v>0.3389820525018686</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18">
       <c r="A143" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B143" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C143" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D143">
         <v>13.72002601623535</v>
@@ -7886,25 +8744,31 @@
       <c r="P143">
         <v>0.01872061691317921</v>
       </c>
-    </row>
-    <row r="144" spans="1:16">
+      <c r="Q143">
+        <v>0.1043222983905345</v>
+      </c>
+      <c r="R143">
+        <v>0.337070754556648</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18">
       <c r="A144" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B144" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C144" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D144">
-        <v>16.54382514953613</v>
+        <v>16.48526382446289</v>
       </c>
       <c r="E144">
         <v>683509869</v>
       </c>
       <c r="F144">
-        <v>11307867760.71835</v>
+        <v>11267840517.08907</v>
       </c>
       <c r="G144">
         <v>9853714</v>
@@ -7916,13 +8780,13 @@
         <v>37908972</v>
       </c>
       <c r="J144">
-        <v>11329331734.71835</v>
+        <v>11289304491.08907</v>
       </c>
       <c r="K144">
         <v>0.1659630296936925</v>
       </c>
       <c r="L144">
-        <v>0.0008697524470753762</v>
+        <v>0.000872836232540081</v>
       </c>
       <c r="M144">
         <v>0.1612252371285615</v>
@@ -7936,16 +8800,22 @@
       <c r="P144">
         <v>0.08026723143379588</v>
       </c>
-    </row>
-    <row r="145" spans="1:16">
+      <c r="Q144">
+        <v>0.1968200172236394</v>
+      </c>
+      <c r="R144">
+        <v>0.3133165281982265</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18">
       <c r="A145" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B145" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C145" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D145">
         <v>9.752986907958984</v>
@@ -7986,16 +8856,22 @@
       <c r="P145">
         <v>0.008004787462578178</v>
       </c>
-    </row>
-    <row r="146" spans="1:16">
+      <c r="Q145">
+        <v>0.1539707661555679</v>
+      </c>
+      <c r="R145">
+        <v>0.1913823640028366</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18">
       <c r="A146" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B146" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C146" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D146">
         <v>8.561361312866211</v>
@@ -8036,25 +8912,31 @@
       <c r="P146">
         <v>0.009771551999876952</v>
       </c>
-    </row>
-    <row r="147" spans="1:16">
+      <c r="Q146">
+        <v>0.2037089925801271</v>
+      </c>
+      <c r="R146">
+        <v>0.153860315944401</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18">
       <c r="A147" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C147" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D147">
-        <v>9.62465763092041</v>
+        <v>9.587991714477539</v>
       </c>
       <c r="E147">
         <v>304920942</v>
       </c>
       <c r="F147">
-        <v>2934759671.24774</v>
+        <v>2923579465.466686</v>
       </c>
       <c r="G147">
         <v>99821</v>
@@ -8066,13 +8948,13 @@
         <v>3180772</v>
       </c>
       <c r="J147">
-        <v>2935427043.24774</v>
+        <v>2924246837.466686</v>
       </c>
       <c r="K147">
         <v>0.02594003758695101</v>
       </c>
       <c r="L147">
-        <v>3.400561435502707E-05</v>
+        <v>3.413562723948305E-05</v>
       </c>
       <c r="M147">
         <v>0.0134618262484705</v>
@@ -8086,16 +8968,22 @@
       <c r="P147">
         <v>0.004901219575987675</v>
       </c>
-    </row>
-    <row r="148" spans="1:16">
+      <c r="Q147">
+        <v>0.1961183769464689</v>
+      </c>
+      <c r="R147">
+        <v>0.1637589271641387</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18">
       <c r="A148" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B148" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C148" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D148">
         <v>2.960000038146973</v>
@@ -8136,16 +9024,22 @@
       <c r="P148">
         <v>-0.03180876186804183</v>
       </c>
-    </row>
-    <row r="149" spans="1:16">
+      <c r="Q148">
+        <v>0.219625042170707</v>
+      </c>
+      <c r="R148">
+        <v>0.2194322617957492</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18">
       <c r="A149" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B149" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C149" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D149">
         <v>2.700000047683716</v>
@@ -8186,25 +9080,31 @@
       <c r="P149">
         <v>-0.01667168825951592</v>
       </c>
-    </row>
-    <row r="150" spans="1:16">
+      <c r="Q149">
+        <v>0.2238626092196445</v>
+      </c>
+      <c r="R149">
+        <v>0.2122125138093803</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18">
       <c r="A150" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C150" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D150">
-        <v>2.819999933242798</v>
+        <v>2.849999904632568</v>
       </c>
       <c r="E150">
         <v>490017</v>
       </c>
       <c r="F150">
-        <v>1381847.907287836</v>
+        <v>1396548.403268337</v>
       </c>
       <c r="G150">
         <v>57000</v>
@@ -8216,13 +9116,13 @@
         <v>4026000</v>
       </c>
       <c r="J150">
-        <v>3974847.907287836</v>
+        <v>3989548.403268337</v>
       </c>
       <c r="K150">
         <v>0.008611572745127662</v>
       </c>
       <c r="L150">
-        <v>0.01434017132969822</v>
+        <v>0.01428733135642725</v>
       </c>
       <c r="M150">
         <v>-0.07724788872329856</v>
@@ -8236,16 +9136,22 @@
       <c r="P150">
         <v>-0.01592177340910254</v>
       </c>
-    </row>
-    <row r="151" spans="1:16">
+      <c r="Q150">
+        <v>0.2283315414938822</v>
+      </c>
+      <c r="R150">
+        <v>0.2209594020375774</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18">
       <c r="A151" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C151" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D151">
         <v>16.4871826171875</v>
@@ -8286,16 +9192,22 @@
       <c r="P151">
         <v>0.0008483036524264355</v>
       </c>
-    </row>
-    <row r="152" spans="1:16">
+      <c r="Q151">
+        <v>0.235319159781737</v>
+      </c>
+      <c r="R151">
+        <v>0.1901785301742596</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18">
       <c r="A152" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C152" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D152">
         <v>11.03725242614746</v>
@@ -8336,25 +9248,31 @@
       <c r="P152">
         <v>0.0007645399579645516</v>
       </c>
-    </row>
-    <row r="153" spans="1:16">
+      <c r="Q152">
+        <v>0.2439569671002989</v>
+      </c>
+      <c r="R152">
+        <v>0.1307231198204588</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18">
       <c r="A153" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B153" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C153" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D153">
-        <v>8.884759902954102</v>
+        <v>9.1595458984375</v>
       </c>
       <c r="E153">
         <v>736060221</v>
       </c>
       <c r="F153">
-        <v>6539718337.700335</v>
+        <v>6741977378.26355</v>
       </c>
       <c r="G153">
         <v>337603</v>
@@ -8366,13 +9284,13 @@
         <v>11064887</v>
       </c>
       <c r="J153">
-        <v>6543341315.700335</v>
+        <v>6745600356.26355</v>
       </c>
       <c r="K153">
         <v>0.0229851649644111</v>
       </c>
       <c r="L153">
-        <v>5.159489375709974E-05</v>
+        <v>5.004788042127675E-05</v>
       </c>
       <c r="M153">
         <v>0.009251156383250908</v>
@@ -8386,16 +9304,22 @@
       <c r="P153">
         <v>0.003262989223653186</v>
       </c>
-    </row>
-    <row r="154" spans="1:16">
+      <c r="Q153">
+        <v>0.2379473122376233</v>
+      </c>
+      <c r="R153">
+        <v>0.138911510682757</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18">
       <c r="A154" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C154" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D154">
         <v>15.64925289154053</v>
@@ -8428,7 +9352,7 @@
         <v>-0.009294246635233646</v>
       </c>
       <c r="N154" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O154">
         <v>25.43550018625809</v>
@@ -8436,16 +9360,22 @@
       <c r="P154">
         <v>-0.004052597325283657</v>
       </c>
-    </row>
-    <row r="155" spans="1:16">
+      <c r="Q154">
+        <v>0</v>
+      </c>
+      <c r="R154">
+        <v>0.354214888902001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18">
       <c r="A155" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C155" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D155">
         <v>13.53999996185303</v>
@@ -8478,7 +9408,7 @@
         <v>-0.01147919508353941</v>
       </c>
       <c r="N155" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O155">
         <v>26.46714958378529</v>
@@ -8486,25 +9416,31 @@
       <c r="P155">
         <v>-0.004627298215136074</v>
       </c>
-    </row>
-    <row r="156" spans="1:16">
+      <c r="Q155">
+        <v>0</v>
+      </c>
+      <c r="R155">
+        <v>0.3892754456373348</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18">
       <c r="A156" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B156" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C156" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D156">
-        <v>13.07999992370605</v>
+        <v>13.14999961853027</v>
       </c>
       <c r="E156">
         <v>1865153386</v>
       </c>
       <c r="F156">
-        <v>24396206146.58009</v>
+        <v>24526766314.40045</v>
       </c>
       <c r="G156">
         <v>546508</v>
@@ -8516,19 +9452,19 @@
         <v>19923819</v>
       </c>
       <c r="J156">
-        <v>24412822034.58009</v>
+        <v>24543382202.40045</v>
       </c>
       <c r="K156">
         <v>0.01495655123890293</v>
       </c>
       <c r="L156">
-        <v>2.238610510599252E-05</v>
+        <v>2.226702071838123E-05</v>
       </c>
       <c r="M156">
         <v>0.01470004319954924</v>
       </c>
       <c r="N156" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O156">
         <v>32.5631902918164</v>
@@ -8536,25 +9472,31 @@
       <c r="P156">
         <v>0.006110535427996918</v>
       </c>
-    </row>
-    <row r="157" spans="1:16">
+      <c r="Q156">
+        <v>0</v>
+      </c>
+      <c r="R156">
+        <v>0.3712885347297776</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18">
       <c r="A157" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C157" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D157">
-        <v>27.36180305480957</v>
+        <v>27.36180114746094</v>
       </c>
       <c r="E157">
         <v>600944748</v>
       </c>
       <c r="F157">
-        <v>16442931841.59817</v>
+        <v>16442930695.38702</v>
       </c>
       <c r="G157">
         <v>193698</v>
@@ -8566,13 +9508,13 @@
         <v>4786841</v>
       </c>
       <c r="J157">
-        <v>16443189719.59817</v>
+        <v>16443188573.38702</v>
       </c>
       <c r="K157">
         <v>0.03839619213676718</v>
       </c>
       <c r="L157">
-        <v>1.177983124339537E-05</v>
+        <v>1.177983206453622E-05</v>
       </c>
       <c r="M157">
         <v>0.0264577411282305</v>
@@ -8586,25 +9528,31 @@
       <c r="P157">
         <v>0.01690566829575502</v>
       </c>
-    </row>
-    <row r="158" spans="1:16">
+      <c r="Q157">
+        <v>0.1043344927345098</v>
+      </c>
+      <c r="R157">
+        <v>0.2177855708948435</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18">
       <c r="A158" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C158" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D158">
-        <v>29.33825492858887</v>
+        <v>29.3382568359375</v>
       </c>
       <c r="E158">
         <v>594832429</v>
       </c>
       <c r="F158">
-        <v>17451345441.79374</v>
+        <v>17451346576.34656</v>
       </c>
       <c r="G158">
         <v>168269</v>
@@ -8616,13 +9564,13 @@
         <v>4687572</v>
       </c>
       <c r="J158">
-        <v>17451729978.79374</v>
+        <v>17451731113.34656</v>
       </c>
       <c r="K158">
         <v>0.03317535171267021</v>
       </c>
       <c r="L158">
-        <v>9.641966739370256E-06</v>
+        <v>9.641966112537279E-06</v>
       </c>
       <c r="M158">
         <v>0.02450565025987867</v>
@@ -8636,25 +9584,31 @@
       <c r="P158">
         <v>0.01538297133249003</v>
       </c>
-    </row>
-    <row r="159" spans="1:16">
+      <c r="Q158">
+        <v>0.1040170456478077</v>
+      </c>
+      <c r="R158">
+        <v>0.2222445114669236</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18">
       <c r="A159" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C159" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D159">
-        <v>27.76973152160645</v>
+        <v>27.49748229980469</v>
       </c>
       <c r="E159">
         <v>592687967</v>
       </c>
       <c r="F159">
-        <v>16458785719.67674</v>
+        <v>16297426881.88972</v>
       </c>
       <c r="G159">
         <v>317309</v>
@@ -8666,13 +9620,13 @@
         <v>4802606</v>
       </c>
       <c r="J159">
-        <v>16459276703.67674</v>
+        <v>16297917865.88972</v>
       </c>
       <c r="K159">
         <v>0.05994211867560578</v>
       </c>
       <c r="L159">
-        <v>1.927842916263254E-05</v>
+        <v>1.946929679061048E-05</v>
       </c>
       <c r="M159">
         <v>0.06059106243568596</v>
@@ -8686,16 +9640,22 @@
       <c r="P159">
         <v>0.03870682402391618</v>
       </c>
-    </row>
-    <row r="160" spans="1:16">
+      <c r="Q159">
+        <v>0.1068085941267038</v>
+      </c>
+      <c r="R159">
+        <v>0.2126127887681774</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18">
       <c r="A160" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B160" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C160" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D160">
         <v>21.7259693145752</v>
@@ -8736,16 +9696,22 @@
       <c r="P160">
         <v>0.01478918528397341</v>
       </c>
-    </row>
-    <row r="161" spans="1:16">
+      <c r="Q160">
+        <v>0.006927453393259001</v>
+      </c>
+      <c r="R160">
+        <v>0.2149431651808397</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18">
       <c r="A161" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C161" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D161">
         <v>19.65156173706055</v>
@@ -8786,25 +9752,31 @@
       <c r="P161">
         <v>0.01391228577079674</v>
       </c>
-    </row>
-    <row r="162" spans="1:16">
+      <c r="Q161">
+        <v>0.007560993172191835</v>
+      </c>
+      <c r="R161">
+        <v>0.2121223445513799</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18">
       <c r="A162" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C162" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D162">
-        <v>20.12900352478027</v>
+        <v>20.17674827575684</v>
       </c>
       <c r="E162">
         <v>1207186302</v>
       </c>
       <c r="F162">
-        <v>24299457328.02446</v>
+        <v>24357094137.39577</v>
       </c>
       <c r="G162">
         <v>127185</v>
@@ -8816,13 +9788,13 @@
         <v>4263750</v>
       </c>
       <c r="J162">
-        <v>24300634542.02446</v>
+        <v>24358271351.39577</v>
       </c>
       <c r="K162">
         <v>0.02337545332040425</v>
       </c>
       <c r="L162">
-        <v>5.233813947535064E-06</v>
+        <v>5.221429639452312E-06</v>
       </c>
       <c r="M162">
         <v>0.02372911169744943</v>
@@ -8836,16 +9808,22 @@
       <c r="P162">
         <v>0.01833045807393493</v>
       </c>
-    </row>
-    <row r="163" spans="1:16">
+      <c r="Q162">
+        <v>0.007483102642231129</v>
+      </c>
+      <c r="R162">
+        <v>0.2136448179564026</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18">
       <c r="A163" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B163" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C163" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D163">
         <v>12.80547332763672</v>
@@ -8886,25 +9864,31 @@
       <c r="P163">
         <v>0.0168619584082602</v>
       </c>
-    </row>
-    <row r="164" spans="1:16">
+      <c r="Q163">
+        <v>0.1063314641439303</v>
+      </c>
+      <c r="R163">
+        <v>0.3744209314410133</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18">
       <c r="A164" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B164" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C164" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D164">
-        <v>12.83108425140381</v>
+        <v>12.83108520507812</v>
       </c>
       <c r="E164">
         <v>545589739</v>
       </c>
       <c r="F164">
-        <v>7000507907.810414</v>
+        <v>7000508428.125336</v>
       </c>
       <c r="G164">
         <v>284418</v>
@@ -8916,13 +9900,13 @@
         <v>5356848</v>
       </c>
       <c r="J164">
-        <v>7005194991.810414</v>
+        <v>7005195512.125336</v>
       </c>
       <c r="K164">
         <v>0.02831739601582329</v>
       </c>
       <c r="L164">
-        <v>4.060101115422275E-05</v>
+        <v>4.060100813855932E-05</v>
       </c>
       <c r="M164">
         <v>0.03240450354387506</v>
@@ -8936,25 +9920,31 @@
       <c r="P164">
         <v>0.01570899953023045</v>
       </c>
-    </row>
-    <row r="165" spans="1:16">
+      <c r="Q164">
+        <v>0.1000575650951182</v>
+      </c>
+      <c r="R164">
+        <v>0.4243759264057272</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18">
       <c r="A165" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C165" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D165">
-        <v>13.45849990844727</v>
+        <v>13.59805774688721</v>
       </c>
       <c r="E165">
         <v>544279739</v>
       </c>
       <c r="F165">
-        <v>7325188817.501202</v>
+        <v>7401147321.382697</v>
       </c>
       <c r="G165">
         <v>293870</v>
@@ -8966,13 +9956,13 @@
         <v>5342603</v>
       </c>
       <c r="J165">
-        <v>7329895753.501202</v>
+        <v>7405854257.382697</v>
       </c>
       <c r="K165">
         <v>0.02924213737565474</v>
       </c>
       <c r="L165">
-        <v>4.009197536808486E-05</v>
+        <v>3.968077007551815E-05</v>
       </c>
       <c r="M165">
         <v>0.03569514710338762</v>
@@ -8986,25 +9976,31 @@
       <c r="P165">
         <v>0.01692488945195237</v>
       </c>
-    </row>
-    <row r="166" spans="1:16">
+      <c r="Q165">
+        <v>0.09688255615042078</v>
+      </c>
+      <c r="R165">
+        <v>0.4180320339731401</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18">
       <c r="A166" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B166" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C166" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D166">
-        <v>25.87369918823242</v>
+        <v>25.86194610595703</v>
       </c>
       <c r="E166">
         <v>9802082</v>
       </c>
       <c r="F166">
-        <v>253616121.0863876</v>
+        <v>253500916.4101715</v>
       </c>
       <c r="G166">
         <v>8080000</v>
@@ -9016,13 +10012,13 @@
         <v>0</v>
       </c>
       <c r="J166">
-        <v>393761121.0863876</v>
+        <v>393645916.4101715</v>
       </c>
       <c r="K166">
         <v>0.0576545720503764</v>
       </c>
       <c r="L166">
-        <v>0.02052005535159811</v>
+        <v>0.02052606076467155</v>
       </c>
       <c r="N166">
         <v>0</v>
@@ -9033,25 +10029,31 @@
       <c r="P166">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:16">
+      <c r="Q166">
+        <v>0.01440677966101695</v>
+      </c>
+      <c r="R166">
+        <v>0.3520012847754114</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18">
       <c r="A167" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B167" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C167" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D167">
-        <v>24.4400577545166</v>
+        <v>24.42896270751953</v>
       </c>
       <c r="E167">
         <v>9792447</v>
       </c>
       <c r="F167">
-        <v>239327970.2380428</v>
+        <v>239219322.5783615</v>
       </c>
       <c r="G167">
         <v>8330000</v>
@@ -9063,13 +10065,13 @@
         <v>0</v>
       </c>
       <c r="J167">
-        <v>382278970.2380428</v>
+        <v>382170322.5783615</v>
       </c>
       <c r="K167">
         <v>0.05827171548292771</v>
       </c>
       <c r="L167">
-        <v>0.02179036946451163</v>
+        <v>0.0217965642747992</v>
       </c>
       <c r="N167">
         <v>0</v>
@@ -9080,25 +10082,31 @@
       <c r="P167">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:16">
+      <c r="Q167">
+        <v>0.009566776288451722</v>
+      </c>
+      <c r="R167">
+        <v>0.3462940317467855</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18">
       <c r="A168" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C168" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D168">
-        <v>27.47728157043457</v>
+        <v>27.95918273925781</v>
       </c>
       <c r="E168">
         <v>9792683</v>
       </c>
       <c r="F168">
-        <v>269076308.1210079</v>
+        <v>273795413.5046234</v>
       </c>
       <c r="G168">
         <v>9390000</v>
@@ -9110,13 +10118,13 @@
         <v>0</v>
       </c>
       <c r="J168">
-        <v>326025308.1210079</v>
+        <v>330744413.5046234</v>
       </c>
       <c r="K168">
         <v>0.1648843702259917</v>
       </c>
       <c r="L168">
-        <v>0.02880144505994853</v>
+        <v>0.02839050220229567</v>
       </c>
       <c r="N168">
         <v>0</v>
@@ -9127,16 +10135,22 @@
       <c r="P168">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:16">
+      <c r="Q168">
+        <v>0.0121788244217598</v>
+      </c>
+      <c r="R168">
+        <v>0.1344817622386463</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18">
       <c r="A169" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B169" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C169" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D169">
         <v>9.676265716552734</v>
@@ -9177,16 +10191,22 @@
       <c r="P169">
         <v>0.0003992195162684243</v>
       </c>
-    </row>
-    <row r="170" spans="1:16">
+      <c r="Q169">
+        <v>0.1534963645789993</v>
+      </c>
+      <c r="R169">
+        <v>0.1679163478407057</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18">
       <c r="A170" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B170" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C170" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D170">
         <v>7.909999847412109</v>
@@ -9227,16 +10247,22 @@
       <c r="P170">
         <v>-0.003896481467550277</v>
       </c>
-    </row>
-    <row r="171" spans="1:16">
+      <c r="Q170">
+        <v>0.1552777709252282</v>
+      </c>
+      <c r="R170">
+        <v>0.1796893798021476</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18">
       <c r="A171" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B171" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C171" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D171">
         <v>6.239999771118164</v>
@@ -9277,25 +10303,31 @@
       <c r="P171">
         <v>0.004574386957627765</v>
       </c>
-    </row>
-    <row r="172" spans="1:16">
+      <c r="Q171">
+        <v>0.1658319821004512</v>
+      </c>
+      <c r="R171">
+        <v>0.179489938049448</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18">
       <c r="A172" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B172" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C172" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D172">
-        <v>7.985350608825684</v>
+        <v>7.970367431640625</v>
       </c>
       <c r="E172">
         <v>10326649</v>
       </c>
       <c r="F172">
-        <v>82461912.87927914</v>
+        <v>82307186.86758423</v>
       </c>
       <c r="G172">
         <v>3594000</v>
@@ -9307,19 +10339,19 @@
         <v>80435000</v>
       </c>
       <c r="J172">
-        <v>83377912.87927914</v>
+        <v>83223186.86758423</v>
       </c>
       <c r="K172">
         <v>0.04417892834753107</v>
       </c>
       <c r="L172">
-        <v>0.04310494081572497</v>
+        <v>0.04318508020749537</v>
       </c>
       <c r="M172">
         <v>0.04320258593895692</v>
       </c>
       <c r="N172" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O172">
         <v>1.297718419588203</v>
@@ -9327,25 +10359,31 @@
       <c r="P172">
         <v>0.03942278239758585</v>
       </c>
-    </row>
-    <row r="173" spans="1:16">
+      <c r="Q172">
+        <v>0</v>
+      </c>
+      <c r="R172">
+        <v>0.05291161355463033</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18">
       <c r="A173" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B173" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C173" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D173">
-        <v>7.55927848815918</v>
+        <v>7.54509162902832</v>
       </c>
       <c r="E173">
         <v>10326896</v>
       </c>
       <c r="F173">
-        <v>78063882.78225708</v>
+        <v>77917376.56344604</v>
       </c>
       <c r="G173">
         <v>3958000</v>
@@ -9357,19 +10395,19 @@
         <v>83551000</v>
       </c>
       <c r="J173">
-        <v>78896882.78225708</v>
+        <v>78750376.56344604</v>
       </c>
       <c r="K173">
         <v>0.04690462646947289</v>
       </c>
       <c r="L173">
-        <v>0.05016674753707893</v>
+        <v>0.05026007712878931</v>
       </c>
       <c r="M173">
         <v>0.04502639106653421</v>
       </c>
       <c r="N173" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O173">
         <v>1.173067205659424</v>
@@ -9377,25 +10415,31 @@
       <c r="P173">
         <v>0.04076855554471862</v>
       </c>
-    </row>
-    <row r="174" spans="1:16">
+      <c r="Q173">
+        <v>0</v>
+      </c>
+      <c r="R173">
+        <v>0.05031589670232019</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18">
       <c r="A174" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C174" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D174">
-        <v>8.577106475830078</v>
+        <v>8.622879981994629</v>
       </c>
       <c r="E174">
         <v>10326896</v>
       </c>
       <c r="F174">
-        <v>88574886.55682373</v>
+        <v>89047584.79454041</v>
       </c>
       <c r="G174">
         <v>4067000</v>
@@ -9407,19 +10451,19 @@
         <v>86463000</v>
       </c>
       <c r="J174">
-        <v>89484886.55682373</v>
+        <v>89957584.79454041</v>
       </c>
       <c r="K174">
         <v>0.04654756045918075</v>
       </c>
       <c r="L174">
-        <v>0.04544901554317127</v>
+        <v>0.04521019555259146</v>
       </c>
       <c r="M174">
         <v>0.04416918219353944</v>
       </c>
       <c r="N174" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O174">
         <v>1.491271207278092</v>
@@ -9427,16 +10471,22 @@
       <c r="P174">
         <v>0.03982979255968212</v>
       </c>
-    </row>
-    <row r="175" spans="1:16">
+      <c r="Q174">
+        <v>0</v>
+      </c>
+      <c r="R174">
+        <v>0.06325417435833255</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18">
       <c r="A175" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C175" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D175">
         <v>25.77401733398438</v>
@@ -9477,16 +10527,22 @@
       <c r="P175">
         <v>0.009629477334730649</v>
       </c>
-    </row>
-    <row r="176" spans="1:16">
+      <c r="Q175">
+        <v>0.4293007562011416</v>
+      </c>
+      <c r="R175">
+        <v>0.1313561733525362</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18">
       <c r="A176" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C176" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D176">
         <v>24.27012252807617</v>
@@ -9527,25 +10583,31 @@
       <c r="P176">
         <v>0.0165877005900517</v>
       </c>
-    </row>
-    <row r="177" spans="1:16">
+      <c r="Q176">
+        <v>0.4516729744053625</v>
+      </c>
+      <c r="R176">
+        <v>0.1622171395117686</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18">
       <c r="A177" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B177" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C177" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D177">
-        <v>24.13286590576172</v>
+        <v>24.33168411254883</v>
       </c>
       <c r="E177">
         <v>1715126309</v>
       </c>
       <c r="F177">
-        <v>41390913226.54104</v>
+        <v>41731911563.70981</v>
       </c>
       <c r="G177">
         <v>673075</v>
@@ -9557,13 +10619,13 @@
         <v>6302638</v>
       </c>
       <c r="J177">
-        <v>41393772648.54104</v>
+        <v>41734770985.70981</v>
       </c>
       <c r="K177">
         <v>0.0734632822749469</v>
       </c>
       <c r="L177">
-        <v>1.626029610093351E-05</v>
+        <v>1.612743964092828E-05</v>
       </c>
       <c r="M177">
         <v>0.05315488530358241</v>
@@ -9577,16 +10639,22 @@
       <c r="P177">
         <v>0.01591256430268869</v>
       </c>
-    </row>
-    <row r="178" spans="1:16">
+      <c r="Q177">
+        <v>0.4336899540752078</v>
+      </c>
+      <c r="R177">
+        <v>0.1515680584444848</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18">
       <c r="A178" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B178" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C178" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D178">
         <v>6.513853549957275</v>
@@ -9627,16 +10695,22 @@
       <c r="P178">
         <v>-0.006246092520169683</v>
       </c>
-    </row>
-    <row r="179" spans="1:16">
+      <c r="Q178">
+        <v>0.1088704081982844</v>
+      </c>
+      <c r="R178">
+        <v>0.75084898314754</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18">
       <c r="A179" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B179" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C179" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D179">
         <v>6.44630241394043</v>
@@ -9677,25 +10751,31 @@
       <c r="P179">
         <v>0.00254196894700633</v>
       </c>
-    </row>
-    <row r="180" spans="1:16">
+      <c r="Q179">
+        <v>0.1076934163484307</v>
+      </c>
+      <c r="R179">
+        <v>0.7259683141657804</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18">
       <c r="A180" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B180" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C180" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D180">
-        <v>6.118197441101074</v>
+        <v>6.262948989868164</v>
       </c>
       <c r="E180">
         <v>588325956</v>
       </c>
       <c r="F180">
-        <v>3599494358.532543</v>
+        <v>3684655451.843422</v>
       </c>
       <c r="G180">
         <v>578422</v>
@@ -9707,13 +10787,13 @@
         <v>744206</v>
       </c>
       <c r="J180">
-        <v>3619920373.532543</v>
+        <v>3705081466.843422</v>
       </c>
       <c r="K180">
         <v>0.02732243560423861</v>
       </c>
       <c r="L180">
-        <v>0.0001597885976247428</v>
+        <v>0.0001561158655150414</v>
       </c>
       <c r="M180">
         <v>0.1156373369739024</v>
@@ -9727,16 +10807,22 @@
       <c r="P180">
         <v>0.00243268760079839</v>
       </c>
-    </row>
-    <row r="181" spans="1:16">
+      <c r="Q180">
+        <v>0.1251816466387411</v>
+      </c>
+      <c r="R180">
+        <v>0.6978851775862231</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18">
       <c r="A181" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B181" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C181" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E181">
         <v>920205</v>
@@ -9765,16 +10851,22 @@
       <c r="P181">
         <v>-0.00374476127306444</v>
       </c>
-    </row>
-    <row r="182" spans="1:16">
+      <c r="Q181">
+        <v>0.1697633215078781</v>
+      </c>
+      <c r="R181">
+        <v>0.1479886108976218</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18">
       <c r="A182" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B182" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C182" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E182">
         <v>920205</v>
@@ -9803,16 +10895,22 @@
       <c r="P182">
         <v>0.03859226968875062</v>
       </c>
-    </row>
-    <row r="183" spans="1:16">
+      <c r="Q182">
+        <v>0.2228115628466529</v>
+      </c>
+      <c r="R182">
+        <v>0.1014777742261906</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18">
       <c r="A183" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B183" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C183" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E183">
         <v>920205</v>
@@ -9841,16 +10939,22 @@
       <c r="P183">
         <v>0.007949168864388593</v>
       </c>
-    </row>
-    <row r="184" spans="1:16">
+      <c r="Q183">
+        <v>0.2018303945886923</v>
+      </c>
+      <c r="R183">
+        <v>0.1432496325585262</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18">
       <c r="A184" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B184" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C184" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E184">
         <v>374921</v>
@@ -9879,16 +10983,22 @@
       <c r="P184">
         <v>0.02409716117339969</v>
       </c>
-    </row>
-    <row r="185" spans="1:16">
+      <c r="Q184">
+        <v>0.0002044928927900026</v>
+      </c>
+      <c r="R184">
+        <v>0.2058289490886632</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18">
       <c r="A185" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B185" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C185" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E185">
         <v>374921</v>
@@ -9917,16 +11027,22 @@
       <c r="P185">
         <v>0.03443855513290822</v>
       </c>
-    </row>
-    <row r="186" spans="1:16">
+      <c r="Q185">
+        <v>0.0001229575238176915</v>
+      </c>
+      <c r="R185">
+        <v>0.2116149137529453</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18">
       <c r="A186" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B186" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C186" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E186">
         <v>374921</v>
@@ -9955,25 +11071,31 @@
       <c r="P186">
         <v>0.03752878807337477</v>
       </c>
-    </row>
-    <row r="187" spans="1:16">
+      <c r="Q186">
+        <v>0.0001547632863408747</v>
+      </c>
+      <c r="R186">
+        <v>0.2153544218076145</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18">
       <c r="A187" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B187" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C187" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D187">
-        <v>7.641429901123047</v>
+        <v>7.641429424285889</v>
       </c>
       <c r="E187">
         <v>2982810591</v>
       </c>
       <c r="F187">
-        <v>22792938039.45391</v>
+        <v>22792936617.13898</v>
       </c>
       <c r="G187">
         <v>514157</v>
@@ -9985,19 +11107,19 @@
         <v>24417580</v>
       </c>
       <c r="J187">
-        <v>22791045538.45391</v>
+        <v>22791044116.13898</v>
       </c>
       <c r="K187">
         <v>0.02282597987780642</v>
       </c>
       <c r="L187">
-        <v>2.255960566321957E-05</v>
+        <v>2.255960707109118E-05</v>
       </c>
       <c r="M187">
         <v>0.02176231223569248</v>
       </c>
       <c r="N187" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O187">
         <v>0</v>
@@ -10005,16 +11127,22 @@
       <c r="P187">
         <v>0.02077448377040247</v>
       </c>
-    </row>
-    <row r="188" spans="1:16">
+      <c r="Q187">
+        <v>0</v>
+      </c>
+      <c r="R187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18">
       <c r="A188" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B188" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C188" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D188">
         <v>7.358827590942383</v>
@@ -10047,7 +11175,7 @@
         <v>0.01906764891084878</v>
       </c>
       <c r="N188" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O188">
         <v>0</v>
@@ -10055,25 +11183,31 @@
       <c r="P188">
         <v>0.01854058837212965</v>
       </c>
-    </row>
-    <row r="189" spans="1:16">
+      <c r="Q188">
+        <v>0</v>
+      </c>
+      <c r="R188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18">
       <c r="A189" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B189" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C189" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D189">
-        <v>8.157734870910645</v>
+        <v>8.068967819213867</v>
       </c>
       <c r="E189">
         <v>2982810591</v>
       </c>
       <c r="F189">
-        <v>24332977971.52229</v>
+        <v>24068202669.58929</v>
       </c>
       <c r="G189">
         <v>610898</v>
@@ -10085,19 +11219,19 @@
         <v>25493448</v>
       </c>
       <c r="J189">
-        <v>24331053162.52229</v>
+        <v>24066277860.58929</v>
       </c>
       <c r="K189">
         <v>0.02591995235702834</v>
       </c>
       <c r="L189">
-        <v>2.51077499983018E-05</v>
+        <v>2.538398349502981E-05</v>
       </c>
       <c r="M189">
         <v>0.04784209652613487</v>
       </c>
       <c r="N189" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O189">
         <v>0</v>
@@ -10105,16 +11239,22 @@
       <c r="P189">
         <v>0.04573393600466226</v>
       </c>
-    </row>
-    <row r="190" spans="1:16">
+      <c r="Q189">
+        <v>0</v>
+      </c>
+      <c r="R189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18">
       <c r="A190" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B190" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C190" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D190">
         <v>35.85073089599609</v>
@@ -10147,7 +11287,7 @@
         <v>0.07628759341103197</v>
       </c>
       <c r="N190" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O190">
         <v>0</v>
@@ -10155,25 +11295,31 @@
       <c r="P190">
         <v>0.07502561702757057</v>
       </c>
-    </row>
-    <row r="191" spans="1:16">
+      <c r="Q190">
+        <v>0</v>
+      </c>
+      <c r="R190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18">
       <c r="A191" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B191" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C191" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D191">
-        <v>39.5953483581543</v>
+        <v>39.59535598754883</v>
       </c>
       <c r="E191">
         <v>4195492941</v>
       </c>
       <c r="F191">
-        <v>166122004533.0723</v>
+        <v>166122036542.1432</v>
       </c>
       <c r="G191">
         <v>1443012</v>
@@ -10185,19 +11331,19 @@
         <v>19299649</v>
       </c>
       <c r="J191">
-        <v>166121294023.0723</v>
+        <v>166121326032.1432</v>
       </c>
       <c r="K191">
         <v>0.07762661842487702</v>
       </c>
       <c r="L191">
-        <v>8.686496264588347E-06</v>
+        <v>8.686494590831694E-06</v>
       </c>
       <c r="M191">
         <v>0.07469850876562574</v>
       </c>
       <c r="N191" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O191">
         <v>0</v>
@@ -10205,25 +11351,31 @@
       <c r="P191">
         <v>0.07216734456129476</v>
       </c>
-    </row>
-    <row r="192" spans="1:16">
+      <c r="Q191">
+        <v>0</v>
+      </c>
+      <c r="R191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18">
       <c r="A192" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B192" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C192" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D192">
-        <v>51.3785285949707</v>
+        <v>52.86154556274414</v>
       </c>
       <c r="E192">
         <v>4195510372</v>
       </c>
       <c r="F192">
-        <v>215559149618.2982</v>
+        <v>221781162688.4436</v>
       </c>
       <c r="G192">
         <v>1573594</v>
@@ -10235,19 +11387,19 @@
         <v>19724495</v>
       </c>
       <c r="J192">
-        <v>215558334921.2982</v>
+        <v>221780347991.4436</v>
       </c>
       <c r="K192">
         <v>0.08321580167064714</v>
       </c>
       <c r="L192">
-        <v>7.300084223486557E-06</v>
+        <v>7.095281499245867E-06</v>
       </c>
       <c r="M192">
         <v>0.08003642171827466</v>
       </c>
       <c r="N192" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O192">
         <v>0</v>
@@ -10255,16 +11407,22 @@
       <c r="P192">
         <v>0.07864015542743191</v>
       </c>
-    </row>
-    <row r="193" spans="1:16">
+      <c r="Q192">
+        <v>0</v>
+      </c>
+      <c r="R192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18">
       <c r="A193" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B193" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C193" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D193">
         <v>5.431755542755127</v>
@@ -10305,25 +11463,31 @@
       <c r="P193">
         <v>0.04853481776136862</v>
       </c>
-    </row>
-    <row r="194" spans="1:16">
+      <c r="Q193">
+        <v>0.1653402996327683</v>
+      </c>
+      <c r="R193">
+        <v>0.2491047962614374</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18">
       <c r="A194" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B194" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C194" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D194">
-        <v>4.639560222625732</v>
+        <v>4.639560699462891</v>
       </c>
       <c r="E194">
         <v>1130819289</v>
       </c>
       <c r="F194">
-        <v>5246504192.222313</v>
+        <v>5246504731.438969</v>
       </c>
       <c r="G194">
         <v>316583</v>
@@ -10335,13 +11499,13 @@
         <v>3730077</v>
       </c>
       <c r="J194">
-        <v>5247369591.222313</v>
+        <v>5247370130.438969</v>
       </c>
       <c r="K194">
         <v>0.06889014326263482</v>
       </c>
       <c r="L194">
-        <v>6.0331751841832E-05</v>
+        <v>6.033174564217681E-05</v>
       </c>
       <c r="M194">
         <v>0.06567880502198749</v>
@@ -10355,25 +11519,31 @@
       <c r="P194">
         <v>0.03616313835939063</v>
       </c>
-    </row>
-    <row r="195" spans="1:16">
+      <c r="Q194">
+        <v>0.1802121043708793</v>
+      </c>
+      <c r="R194">
+        <v>0.2438165501635177</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18">
       <c r="A195" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B195" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C195" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D195">
-        <v>5.909455299377441</v>
+        <v>5.983788013458252</v>
       </c>
       <c r="E195">
         <v>1130408858</v>
       </c>
       <c r="F195">
-        <v>6680100616.371302</v>
+        <v>6764126974.807431</v>
       </c>
       <c r="G195">
         <v>381502</v>
@@ -10385,13 +11555,13 @@
         <v>3874740</v>
       </c>
       <c r="J195">
-        <v>6680691826.371302</v>
+        <v>6764718184.807431</v>
       </c>
       <c r="K195">
         <v>0.08542460170848308</v>
       </c>
       <c r="L195">
-        <v>5.710516364399006E-05</v>
+        <v>5.639584526326577E-05</v>
       </c>
       <c r="M195">
         <v>0.08586434186551872</v>
@@ -10405,25 +11575,31 @@
       <c r="P195">
         <v>0.04704624333692317</v>
       </c>
-    </row>
-    <row r="196" spans="1:16">
+      <c r="Q195">
+        <v>0.2061337072499706</v>
+      </c>
+      <c r="R195">
+        <v>0.2442474399757459</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18">
       <c r="A196" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B196" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C196" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D196">
-        <v>15.50505256652832</v>
+        <v>15.50505352020264</v>
       </c>
       <c r="E196">
         <v>439840526</v>
       </c>
       <c r="F196">
-        <v>6819750476.519466</v>
+        <v>6819750895.984079</v>
       </c>
       <c r="G196">
         <v>501253</v>
@@ -10435,13 +11611,13 @@
         <v>4943787</v>
       </c>
       <c r="J196">
-        <v>6823240624.519466</v>
+        <v>6823241043.984079</v>
       </c>
       <c r="K196">
         <v>0.05943287445302815</v>
       </c>
       <c r="L196">
-        <v>7.346260048322732E-05</v>
+        <v>7.346259596705076E-05</v>
       </c>
       <c r="M196">
         <v>0.04510530085539689</v>
@@ -10455,16 +11631,22 @@
       <c r="P196">
         <v>0.01487743600326036</v>
       </c>
-    </row>
-    <row r="197" spans="1:16">
+      <c r="Q196">
+        <v>0.09941523979291642</v>
+      </c>
+      <c r="R196">
+        <v>0.3027123327646988</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18">
       <c r="A197" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B197" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C197" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D197">
         <v>14.30035209655762</v>
@@ -10505,25 +11687,31 @@
       <c r="P197">
         <v>0.02126832395683619</v>
       </c>
-    </row>
-    <row r="198" spans="1:16">
+      <c r="Q197">
+        <v>0.1000093789326589</v>
+      </c>
+      <c r="R197">
+        <v>0.3195178511244556</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18">
       <c r="A198" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B198" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C198" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D198">
-        <v>14.91497993469238</v>
+        <v>15.29195308685303</v>
       </c>
       <c r="E198">
         <v>439928708</v>
       </c>
       <c r="F198">
-        <v>6561527852.515144</v>
+        <v>6727369164.295864</v>
       </c>
       <c r="G198">
         <v>136797</v>
@@ -10535,13 +11723,13 @@
         <v>4957971</v>
       </c>
       <c r="J198">
-        <v>6565545820.515144</v>
+        <v>6731387132.295864</v>
       </c>
       <c r="K198">
         <v>0.01524041105894325</v>
       </c>
       <c r="L198">
-        <v>2.083558682547838E-05</v>
+        <v>2.032226007975014E-05</v>
       </c>
       <c r="M198">
         <v>0.0001728529674739929</v>
@@ -10555,16 +11743,22 @@
       <c r="P198">
         <v>5.394007716892767E-05</v>
       </c>
-    </row>
-    <row r="199" spans="1:16">
+      <c r="Q198">
+        <v>0.09043900488173434</v>
+      </c>
+      <c r="R198">
+        <v>0.3176060978344601</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18">
       <c r="A199" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B199" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C199" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D199">
         <v>19.6641902923584</v>
@@ -10605,16 +11799,22 @@
       <c r="P199">
         <v>0.007906021708455759</v>
       </c>
-    </row>
-    <row r="200" spans="1:16">
+      <c r="Q199">
+        <v>0.0795555824586034</v>
+      </c>
+      <c r="R199">
+        <v>0.6224181759963947</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18">
       <c r="A200" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B200" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C200" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D200">
         <v>18.59745025634766</v>
@@ -10655,25 +11855,31 @@
       <c r="P200">
         <v>0.005267463855672073</v>
       </c>
-    </row>
-    <row r="201" spans="1:16">
+      <c r="Q200">
+        <v>0.08870083103895697</v>
+      </c>
+      <c r="R200">
+        <v>0.6653055287497339</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18">
       <c r="A201" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B201" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C201" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D201">
-        <v>18.41004943847656</v>
+        <v>18.56868171691895</v>
       </c>
       <c r="E201">
         <v>6079346892</v>
       </c>
       <c r="F201">
-        <v>111921076835.3688</v>
+        <v>112885457484.2884</v>
       </c>
       <c r="G201">
         <v>1358119</v>
@@ -10685,13 +11891,13 @@
         <v>9989390</v>
       </c>
       <c r="J201">
-        <v>111952657249.3688</v>
+        <v>112917037898.2884</v>
       </c>
       <c r="K201">
         <v>0.03267080595328282</v>
       </c>
       <c r="L201">
-        <v>1.21311903921571E-05</v>
+        <v>1.202758259761777E-05</v>
       </c>
       <c r="M201">
         <v>0.07193512316567878</v>
@@ -10705,16 +11911,22 @@
       <c r="P201">
         <v>0.0127545542071305</v>
       </c>
-    </row>
-    <row r="202" spans="1:16">
+      <c r="Q201">
+        <v>0.08994132540845651</v>
+      </c>
+      <c r="R201">
+        <v>0.6479137036519476</v>
+      </c>
+    </row>
+    <row r="202" spans="1:18">
       <c r="A202" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B202" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C202" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D202">
         <v>7.044373989105225</v>
@@ -10747,7 +11959,7 @@
         <v>0.03875654869617796</v>
       </c>
       <c r="N202" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O202">
         <v>0</v>
@@ -10755,16 +11967,22 @@
       <c r="P202">
         <v>0.03874534606959026</v>
       </c>
-    </row>
-    <row r="203" spans="1:16">
+      <c r="Q202">
+        <v>0</v>
+      </c>
+      <c r="R202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18">
       <c r="A203" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B203" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C203" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D203">
         <v>7.413849830627441</v>
@@ -10797,7 +12015,7 @@
         <v>0.01550206341149279</v>
       </c>
       <c r="N203" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O203">
         <v>0</v>
@@ -10805,25 +12023,31 @@
       <c r="P203">
         <v>0.01549696706545002</v>
       </c>
-    </row>
-    <row r="204" spans="1:16">
+      <c r="Q203">
+        <v>0</v>
+      </c>
+      <c r="R203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18">
       <c r="A204" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B204" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C204" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D204">
-        <v>7.6620192527771</v>
+        <v>7.626936435699463</v>
       </c>
       <c r="E204">
         <v>1023786904</v>
       </c>
       <c r="F204">
-        <v>7844274969.18906</v>
+        <v>7808357640.509548</v>
       </c>
       <c r="G204">
         <v>450356</v>
@@ -10835,19 +12059,19 @@
         <v>18902252</v>
       </c>
       <c r="J204">
-        <v>7844061887.18906</v>
+        <v>7808144558.509548</v>
       </c>
       <c r="K204">
         <v>0.02409716429354541</v>
       </c>
       <c r="L204">
-        <v>5.741362147276304E-05</v>
+        <v>5.767772312939425E-05</v>
       </c>
       <c r="M204">
         <v>0.0242442540708906</v>
       </c>
       <c r="N204" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O204">
         <v>0</v>
@@ -10855,16 +12079,22 @@
       <c r="P204">
         <v>0.02423712356368238</v>
       </c>
-    </row>
-    <row r="205" spans="1:16">
+      <c r="Q204">
+        <v>0</v>
+      </c>
+      <c r="R204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18">
       <c r="A205" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B205" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C205" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D205">
         <v>13.89314746856689</v>
@@ -10905,25 +12135,31 @@
       <c r="P205">
         <v>0.009286626371044505</v>
       </c>
-    </row>
-    <row r="206" spans="1:16">
+      <c r="Q205">
+        <v>0.1481598708235274</v>
+      </c>
+      <c r="R205">
+        <v>0.03380972226084703</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18">
       <c r="A206" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B206" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C206" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D206">
-        <v>10.33854579925537</v>
+        <v>10.33854484558105</v>
       </c>
       <c r="E206">
         <v>956120</v>
       </c>
       <c r="F206">
-        <v>9884890.409584045</v>
+        <v>9884889.497756958</v>
       </c>
       <c r="G206">
         <v>353344</v>
@@ -10935,13 +12171,13 @@
         <v>10317141</v>
       </c>
       <c r="J206">
-        <v>8604534.409584045</v>
+        <v>8604533.497756958</v>
       </c>
       <c r="K206">
         <v>0.03910063147457862</v>
       </c>
       <c r="L206">
-        <v>0.04106485989601396</v>
+        <v>0.04106486424767946</v>
       </c>
       <c r="M206">
         <v>0.0305301633466093</v>
@@ -10955,25 +12191,31 @@
       <c r="P206">
         <v>0.02054055308933221</v>
       </c>
-    </row>
-    <row r="207" spans="1:16">
+      <c r="Q206">
+        <v>0.1828667043414762</v>
+      </c>
+      <c r="R206">
+        <v>0.03401205811276332</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18">
       <c r="A207" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B207" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C207" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D207">
-        <v>15.0976095199585</v>
+        <v>14.90533638000488</v>
       </c>
       <c r="E207">
         <v>956120</v>
       </c>
       <c r="F207">
-        <v>14435126.41422272</v>
+        <v>14251290.21965027</v>
       </c>
       <c r="G207">
         <v>253764</v>
@@ -10985,13 +12227,13 @@
         <v>10394696</v>
       </c>
       <c r="J207">
-        <v>12900626.41422272</v>
+        <v>12716790.21965027</v>
       </c>
       <c r="K207">
         <v>0.0286409013976666</v>
       </c>
       <c r="L207">
-        <v>0.01967067271401872</v>
+        <v>0.01995503547804683</v>
       </c>
       <c r="M207">
         <v>0.0245573319315928</v>
@@ -11004,6 +12246,12 @@
       </c>
       <c r="P207">
         <v>0.01661966466516161</v>
+      </c>
+      <c r="Q207">
+        <v>0.1732294004762595</v>
+      </c>
+      <c r="R207">
+        <v>0.03299094521063006</v>
       </c>
     </row>
   </sheetData>
